--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -1830,7 +1830,7 @@
       <c r="K25" s="7" t="inlineStr">
         <is>
           <t>pos 38
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -1879,11 +1879,7 @@
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr"/>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="K26" s="9" t="inlineStr"/>
       <c r="L26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1925,11 +1921,7 @@
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr"/>
-      <c r="K27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="K27" s="9" t="inlineStr"/>
       <c r="L27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2653,7 +2645,7 @@
       <c r="K42" s="7" t="inlineStr">
         <is>
           <t>pos 38
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
@@ -2698,11 +2690,7 @@
           <t>ENTER</t>
         </is>
       </c>
-      <c r="K43" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="K43" s="9" t="inlineStr"/>
       <c r="L43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
@@ -2740,11 +2728,7 @@
           <t>L3</t>
         </is>
       </c>
-      <c r="K44" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="K44" s="9" t="inlineStr"/>
       <c r="L44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
@@ -3131,7 +3115,7 @@
       <c r="K53" s="7" t="inlineStr">
         <is>
           <t>pos 38
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -3168,11 +3152,7 @@
       <c r="H54" s="9" t="inlineStr"/>
       <c r="I54" s="9" t="inlineStr"/>
       <c r="J54" s="9" t="inlineStr"/>
-      <c r="K54" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="K54" s="9" t="inlineStr"/>
       <c r="L54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
@@ -7040,7 +7020,7 @@
       <c r="K25" s="7" t="inlineStr">
         <is>
           <t>pos 38
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -7089,11 +7069,7 @@
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr"/>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="K26" s="9" t="inlineStr"/>
       <c r="L26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
@@ -7135,11 +7111,7 @@
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr"/>
-      <c r="K27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="K27" s="9" t="inlineStr"/>
       <c r="L27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
@@ -7898,7 +7870,7 @@
       <c r="K42" s="7" t="inlineStr">
         <is>
           <t>pos 38
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
@@ -7943,11 +7915,7 @@
           <t>&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
-      <c r="K43" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="K43" s="9" t="inlineStr"/>
       <c r="L43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
@@ -7985,11 +7953,7 @@
           <t>&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
-      <c r="K44" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="K44" s="9" t="inlineStr"/>
       <c r="L44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
@@ -8388,7 +8352,7 @@
       <c r="K53" s="7" t="inlineStr">
         <is>
           <t>pos 38
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -8425,11 +8389,7 @@
       <c r="H54" s="9" t="inlineStr"/>
       <c r="I54" s="9" t="inlineStr"/>
       <c r="J54" s="9" t="inlineStr"/>
-      <c r="K54" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="K54" s="9" t="inlineStr"/>
       <c r="L54" s="9" t="inlineStr"/>
     </row>
     <row r="55">

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -5054,7 +5054,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -5109,7 +5109,7 @@
       <c r="L97" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -5119,7 +5119,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr"/>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
       <c r="C98" s="9" t="inlineStr"/>
       <c r="D98" s="9" t="inlineStr">
         <is>
@@ -5137,7 +5141,11 @@
         </is>
       </c>
       <c r="K98" s="9" t="inlineStr"/>
-      <c r="L98" s="9" t="inlineStr"/>
+      <c r="L98" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
@@ -5148,7 +5156,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -5213,7 +5221,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr"/>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
       <c r="C100" s="9" t="inlineStr"/>
       <c r="D100" s="9" t="inlineStr"/>
       <c r="E100" s="9" t="inlineStr"/>
@@ -5240,19 +5252,19 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 31
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
@@ -5300,9 +5312,21 @@
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr"/>
-      <c r="C102" s="9" t="inlineStr"/>
-      <c r="D102" s="9" t="inlineStr"/>
-      <c r="E102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>LWin</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>LAlt</t>
+        </is>
+      </c>
       <c r="F102" s="9" t="inlineStr"/>
       <c r="G102" s="9" t="inlineStr"/>
       <c r="H102" s="9" t="inlineStr"/>
@@ -5424,7 +5448,7 @@
       <c r="B106" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -5479,7 +5503,7 @@
       <c r="L106" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5513,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr"/>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
           <t>🖱右</t>
@@ -5515,7 +5543,11 @@
           <t>🖱右</t>
         </is>
       </c>
-      <c r="L107" s="9" t="inlineStr"/>
+      <c r="L107" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
@@ -5526,7 +5558,7 @@
       <c r="B108" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -5591,7 +5623,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr"/>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
           <t>🖱進</t>
@@ -5630,19 +5666,19 @@
       <c r="C110" s="7" t="inlineStr">
         <is>
           <t>pos 31
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
@@ -5694,9 +5730,21 @@
           <t>🖱進</t>
         </is>
       </c>
-      <c r="C111" s="9" t="inlineStr"/>
-      <c r="D111" s="9" t="inlineStr"/>
-      <c r="E111" s="9" t="inlineStr"/>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>LWin</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>LAlt</t>
+        </is>
+      </c>
       <c r="F111" s="9" t="inlineStr"/>
       <c r="G111" s="9" t="inlineStr"/>
       <c r="H111" s="9" t="inlineStr"/>
@@ -10296,7 +10344,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -10351,7 +10399,7 @@
       <c r="L97" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -10361,7 +10409,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr"/>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
       <c r="C98" s="9" t="inlineStr"/>
       <c r="D98" s="9" t="inlineStr">
         <is>
@@ -10379,7 +10431,11 @@
         </is>
       </c>
       <c r="K98" s="9" t="inlineStr"/>
-      <c r="L98" s="9" t="inlineStr"/>
+      <c r="L98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
@@ -10390,7 +10446,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -10455,7 +10511,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr"/>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
       <c r="C100" s="9" t="inlineStr"/>
       <c r="D100" s="9" t="inlineStr"/>
       <c r="E100" s="9" t="inlineStr"/>
@@ -10482,19 +10542,19 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 31
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
@@ -10542,9 +10602,21 @@
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr"/>
-      <c r="C102" s="9" t="inlineStr"/>
-      <c r="D102" s="9" t="inlineStr"/>
-      <c r="E102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_WIN</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_ALT</t>
+        </is>
+      </c>
       <c r="F102" s="9" t="inlineStr"/>
       <c r="G102" s="9" t="inlineStr"/>
       <c r="H102" s="9" t="inlineStr"/>
@@ -10666,7 +10738,7 @@
       <c r="B106" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -10721,7 +10793,7 @@
       <c r="L106" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10803,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr"/>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB2</t>
@@ -10757,7 +10833,11 @@
           <t>&amp;mkp MB2</t>
         </is>
       </c>
-      <c r="L107" s="9" t="inlineStr"/>
+      <c r="L107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
@@ -10768,7 +10848,7 @@
       <c r="B108" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -10833,7 +10913,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr"/>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB5</t>
@@ -10872,19 +10956,19 @@
       <c r="C110" s="7" t="inlineStr">
         <is>
           <t>pos 31
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
@@ -10936,9 +11020,21 @@
           <t>&amp;mkp MB5</t>
         </is>
       </c>
-      <c r="C111" s="9" t="inlineStr"/>
-      <c r="D111" s="9" t="inlineStr"/>
-      <c r="E111" s="9" t="inlineStr"/>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_WIN</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_ALT</t>
+        </is>
+      </c>
       <c r="F111" s="9" t="inlineStr"/>
       <c r="G111" s="9" t="inlineStr"/>
       <c r="H111" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -5054,7 +5054,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp LCTRL</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -5109,7 +5109,7 @@
       <c r="L97" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;kp RCTRL</t>
+&amp;trans</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>LCtrl</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr"/>
@@ -5143,7 +5143,7 @@
       <c r="K98" s="9" t="inlineStr"/>
       <c r="L98" s="9" t="inlineStr">
         <is>
-          <t>RCtrl</t>
+          <t>▽</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;kp LEFT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>LShift</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr"/>
@@ -5252,19 +5252,19 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 31
-&amp;kp RIGHT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;kp LEFT_WIN</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;kp LEFT_ALT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
@@ -5314,17 +5314,17 @@
       <c r="B102" s="9" t="inlineStr"/>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>RShift</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>LWin</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>LAlt</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr"/>
@@ -10344,7 +10344,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp LCTRL</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -10399,7 +10399,7 @@
       <c r="L97" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;kp RCTRL</t>
+&amp;trans</t>
         </is>
       </c>
     </row>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LCTRL</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr"/>
@@ -10433,7 +10433,7 @@
       <c r="K98" s="9" t="inlineStr"/>
       <c r="L98" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp RCTRL</t>
+          <t>▽</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10446,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;kp LEFT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LEFT_SHIFT</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr"/>
@@ -10542,19 +10542,19 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 31
-&amp;kp RIGHT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;kp LEFT_WIN</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;kp LEFT_ALT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
@@ -10604,17 +10604,17 @@
       <c r="B102" s="9" t="inlineStr"/>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp RIGHT_SHIFT</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LEFT_WIN</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LEFT_ALT</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:N111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -547,12 +547,14 @@
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="3" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -593,12 +595,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -617,6 +619,16 @@
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>10</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -636,7 +648,9 @@
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
-      <c r="L4" s="5" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="5" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -675,31 +689,33 @@
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp Y</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp U</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp I</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp O</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp P</t>
@@ -738,27 +754,29 @@
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>P</t>
         </is>
@@ -801,31 +819,33 @@
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp H</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp J</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp K</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp L</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;mt RCTRL MINUS</t>
@@ -864,27 +884,29 @@
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -922,16 +944,8 @@
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="H9" s="9" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr"/>
       <c r="J9" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -943,6 +957,16 @@
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -984,13 +1008,13 @@
 &amp;kp B</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
+      <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -1015,6 +1039,18 @@
 &amp;kp COMMA</t>
         </is>
       </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;kp PERIOD</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;mt RIGHT_SHIFT SLASH</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -1047,12 +1083,12 @@
           <t>B</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr"/>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>L7</t>
         </is>
       </c>
+      <c r="H11" s="9" t="inlineStr"/>
       <c r="I11" s="9" t="inlineStr">
         <is>
           <t>L7</t>
@@ -1071,6 +1107,16 @@
       <c r="L11" s="9" t="inlineStr">
         <is>
           <t>,</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1151,12 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr"/>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr"/>
       <c r="I12" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -1129,6 +1175,16 @@
       <c r="L12" s="9" t="inlineStr">
         <is>
           <t>〃</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
         </is>
       </c>
     </row>
@@ -1140,41 +1196,31 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>pos 30
-&amp;kp PERIOD</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;mt RIGHT_SHIFT SLASH</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
           <t>pos 32
 &amp;kp LEFT_WIN</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;kp LEFT_ALT</t>
         </is>
       </c>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;mo NUM_SYMBOL</t>
         </is>
       </c>
+      <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -1187,13 +1233,15 @@
 &amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;mo FUNCTION</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;mo FUNCTION</t>
@@ -1208,35 +1256,27 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>LWin</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>LWin</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
           <t>LAlt</t>
         </is>
       </c>
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="9" t="inlineStr"/>
       <c r="F14" s="9" t="inlineStr">
         <is>
           <t>SPACE</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr"/>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
+      <c r="H14" s="9" t="inlineStr"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
           <t>L2</t>
@@ -1247,12 +1287,14 @@
           <t>ENTER</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr"/>
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>L6</t>
         </is>
       </c>
-      <c r="L14" s="9" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>L6</t>
         </is>
@@ -1271,30 +1313,22 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>RShift</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
       <c r="F15" s="9" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr"/>
       <c r="I15" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -1305,12 +1339,14 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr"/>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -1332,7 +1368,9 @@
       <c r="I16" s="4" t="n"/>
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
-      <c r="L16" s="5" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="5" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -1371,31 +1409,33 @@
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp N6</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp N7</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp N8</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp N9</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="N17" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp N0</t>
@@ -1434,27 +1474,29 @@
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr"/>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr"/>
+      <c r="I18" s="9" t="inlineStr"/>
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="L18" s="9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="M18" s="9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="L18" s="9" t="inlineStr">
+      <c r="N18" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1497,31 +1539,33 @@
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp BACKSPACE</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp SEMICOLON</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp SINGLE_QUOTE</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp BACKSLASH</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="N19" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;trans</t>
@@ -1560,27 +1604,29 @@
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr"/>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>;</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>\</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr">
+      <c r="N20" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -1618,16 +1664,8 @@
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr"/>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="H21" s="9" t="inlineStr"/>
+      <c r="I21" s="9" t="inlineStr"/>
       <c r="J21" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -1639,6 +1677,16 @@
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -1680,13 +1728,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -1708,6 +1756,18 @@
       <c r="L22" s="7" t="inlineStr">
         <is>
           <t>pos 29
+&amp;trans</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;trans</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
 &amp;trans</t>
         </is>
       </c>
@@ -1741,6 +1801,16 @@
           <t>▽</t>
         </is>
       </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>▽</t>
+        </is>
+      </c>
+      <c r="N23" s="9" t="inlineStr">
+        <is>
+          <t>▽</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -1771,6 +1841,16 @@
           <t>〃</t>
         </is>
       </c>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -1780,41 +1860,31 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>pos 30
-&amp;trans</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;trans</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
           <t>pos 32
 &amp;trans</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;trans</t>
         </is>
       </c>
+      <c r="D25" s="7" t="inlineStr"/>
+      <c r="E25" s="7" t="inlineStr"/>
       <c r="F25" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
+      <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -1827,13 +1897,15 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="K25" s="7" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="N25" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -1856,16 +1928,8 @@
           <t>▽</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="D26" s="9" t="inlineStr"/>
+      <c r="E26" s="9" t="inlineStr"/>
       <c r="F26" s="9" t="inlineStr">
         <is>
           <t>SPACE</t>
@@ -1881,6 +1945,8 @@
       <c r="J26" s="9" t="inlineStr"/>
       <c r="K26" s="9" t="inlineStr"/>
       <c r="L26" s="9" t="inlineStr"/>
+      <c r="M26" s="9" t="inlineStr"/>
+      <c r="N26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -1898,16 +1964,8 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="D27" s="9" t="inlineStr"/>
+      <c r="E27" s="9" t="inlineStr"/>
       <c r="F27" s="9" t="inlineStr">
         <is>
           <t>L3</t>
@@ -1923,6 +1981,8 @@
       <c r="J27" s="9" t="inlineStr"/>
       <c r="K27" s="9" t="inlineStr"/>
       <c r="L27" s="9" t="inlineStr"/>
+      <c r="M27" s="9" t="inlineStr"/>
+      <c r="N27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1940,7 +2000,9 @@
       <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
-      <c r="L28" s="5" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="5" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
@@ -1979,31 +2041,33 @@
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;mm_vim_y</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;mm_vim_u</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;mm_vim_o</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp LC(V)</t>
@@ -2031,19 +2095,21 @@
       <c r="F30" s="9" t="inlineStr"/>
       <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="9" t="inlineStr"/>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr"/>
+      <c r="J30" s="9" t="inlineStr"/>
+      <c r="K30" s="9" t="inlineStr">
         <is>
           <t>⌃Z</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr"/>
-      <c r="K30" s="10" t="inlineStr">
+      <c r="L30" s="9" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>END
 ▸ ENTER</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr">
+      <c r="N30" s="9" t="inlineStr">
         <is>
           <t>⌃V</t>
         </is>
@@ -2069,25 +2135,27 @@
       <c r="E31" s="9" t="inlineStr"/>
       <c r="F31" s="9" t="inlineStr"/>
       <c r="G31" s="9" t="inlineStr"/>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr"/>
+      <c r="I31" s="9" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>HOME
 ▸ ⇧END
 ▸ ⌃C</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr"/>
       <c r="K31" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="L31" s="9" t="inlineStr">
+      <c r="L31" s="9" t="inlineStr"/>
+      <c r="M31" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N31" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2113,26 +2181,28 @@
       <c r="E32" s="9" t="inlineStr"/>
       <c r="F32" s="9" t="inlineStr"/>
       <c r="G32" s="9" t="inlineStr"/>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H32" s="9" t="inlineStr"/>
+      <c r="I32" s="9" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>⇧END
 ▸ ⌃C</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="J32" s="9" t="inlineStr"/>
-      <c r="K32" s="10" t="inlineStr">
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>HOME
 ▸ ENTER
 ▸ ↑</t>
         </is>
       </c>
-      <c r="L32" s="9" t="inlineStr">
+      <c r="N32" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2163,18 +2233,20 @@
       <c r="F33" s="9" t="inlineStr"/>
       <c r="G33" s="9" t="inlineStr"/>
       <c r="H33" s="9" t="inlineStr"/>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>PgUp</t>
-        </is>
-      </c>
+      <c r="I33" s="9" t="inlineStr"/>
       <c r="J33" s="9" t="inlineStr"/>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L33" s="9" t="inlineStr">
+          <t>PgUp</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr"/>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N33" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2217,31 +2289,33 @@
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr"/>
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LEFT</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;mm_vim_j</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp UP_ARROW</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp RIGHT</t>
         </is>
       </c>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="N34" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -2264,27 +2338,29 @@
       <c r="E35" s="9" t="inlineStr"/>
       <c r="F35" s="9" t="inlineStr"/>
       <c r="G35" s="9" t="inlineStr"/>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr"/>
+      <c r="I35" s="9" t="inlineStr"/>
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>←</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="L35" s="9" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="M35" s="9" t="inlineStr">
         <is>
           <t>→</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr">
+      <c r="N35" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -2316,16 +2392,8 @@
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="H36" s="9" t="inlineStr"/>
+      <c r="I36" s="9" t="inlineStr"/>
       <c r="J36" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -2337,6 +2405,16 @@
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M36" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N36" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2367,29 +2445,31 @@
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr"/>
-      <c r="H37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="H37" s="9" t="inlineStr"/>
+      <c r="I37" s="9" t="inlineStr"/>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>END
 ▸ DEL
 ▸ SPACE</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
       <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N37" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2415,16 +2495,8 @@
       <c r="E38" s="9" t="inlineStr"/>
       <c r="F38" s="9" t="inlineStr"/>
       <c r="G38" s="9" t="inlineStr"/>
-      <c r="H38" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="H38" s="9" t="inlineStr"/>
+      <c r="I38" s="9" t="inlineStr"/>
       <c r="J38" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -2436,6 +2508,16 @@
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M38" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N38" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2477,13 +2559,13 @@
 &amp;kp LC(LEFT)</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr"/>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -2506,6 +2588,18 @@
         <is>
           <t>pos 29
 &amp;none</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -2546,6 +2640,12 @@
       </c>
       <c r="K40" s="9" t="inlineStr"/>
       <c r="L40" s="9" t="inlineStr"/>
+      <c r="M40" s="9" t="inlineStr"/>
+      <c r="N40" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="45" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
@@ -2586,6 +2686,12 @@
       </c>
       <c r="K41" s="9" t="inlineStr"/>
       <c r="L41" s="9" t="inlineStr"/>
+      <c r="M41" s="9" t="inlineStr"/>
+      <c r="N41" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
@@ -2595,41 +2701,31 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>pos 30
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
           <t>pos 32
 &amp;trans</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;trans</t>
         </is>
       </c>
+      <c r="D42" s="7" t="inlineStr"/>
+      <c r="E42" s="7" t="inlineStr"/>
       <c r="F42" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
+      <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -2642,13 +2738,15 @@
 &amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
-      <c r="K42" s="7" t="inlineStr">
+      <c r="K42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L42" s="7" t="inlineStr">
+      <c r="N42" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -2661,29 +2759,25 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr"/>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>▽</t>
+        </is>
+      </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>RShift</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="D43" s="9" t="inlineStr"/>
+      <c r="E43" s="9" t="inlineStr"/>
       <c r="F43" s="9" t="inlineStr"/>
-      <c r="G43" s="9" t="inlineStr"/>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
+      <c r="H43" s="9" t="inlineStr"/>
       <c r="I43" s="9" t="inlineStr"/>
       <c r="J43" s="9" t="inlineStr">
         <is>
@@ -2692,6 +2786,8 @@
       </c>
       <c r="K43" s="9" t="inlineStr"/>
       <c r="L43" s="9" t="inlineStr"/>
+      <c r="M43" s="9" t="inlineStr"/>
+      <c r="N43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -2699,29 +2795,25 @@
           <t>ホールド</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr"/>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr"/>
       <c r="F44" s="9" t="inlineStr"/>
-      <c r="G44" s="9" t="inlineStr"/>
-      <c r="H44" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr"/>
       <c r="I44" s="9" t="inlineStr"/>
       <c r="J44" s="9" t="inlineStr">
         <is>
@@ -2730,6 +2822,8 @@
       </c>
       <c r="K44" s="9" t="inlineStr"/>
       <c r="L44" s="9" t="inlineStr"/>
+      <c r="M44" s="9" t="inlineStr"/>
+      <c r="N44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2747,7 +2841,9 @@
       <c r="I45" s="4" t="n"/>
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
-      <c r="L45" s="5" t="n"/>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="n"/>
+      <c r="N45" s="5" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
@@ -2786,31 +2882,33 @@
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr"/>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr"/>
+      <c r="I46" s="7" t="inlineStr"/>
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;mm_vim_shift_6</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="K46" s="7" t="inlineStr">
+      <c r="M46" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="L46" s="7" t="inlineStr">
+      <c r="N46" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp HOME</t>
@@ -2833,7 +2931,9 @@
       <c r="I47" s="9" t="inlineStr"/>
       <c r="J47" s="9" t="inlineStr"/>
       <c r="K47" s="9" t="inlineStr"/>
-      <c r="L47" s="9" t="inlineStr">
+      <c r="L47" s="9" t="inlineStr"/>
+      <c r="M47" s="9" t="inlineStr"/>
+      <c r="N47" s="9" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
@@ -2855,15 +2955,17 @@
       </c>
       <c r="F48" s="9" t="inlineStr"/>
       <c r="G48" s="9" t="inlineStr"/>
-      <c r="H48" s="9" t="inlineStr">
+      <c r="H48" s="9" t="inlineStr"/>
+      <c r="I48" s="9" t="inlineStr"/>
+      <c r="J48" s="9" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr"/>
-      <c r="J48" s="9" t="inlineStr"/>
       <c r="K48" s="9" t="inlineStr"/>
-      <c r="L48" s="9" t="inlineStr">
+      <c r="L48" s="9" t="inlineStr"/>
+      <c r="M48" s="9" t="inlineStr"/>
+      <c r="N48" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2906,31 +3008,33 @@
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr"/>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr"/>
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LEFT</t>
         </is>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="K49" s="7" t="inlineStr">
+      <c r="M49" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="L49" s="7" t="inlineStr">
+      <c r="N49" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -2953,15 +3057,17 @@
       <c r="E50" s="9" t="inlineStr"/>
       <c r="F50" s="9" t="inlineStr"/>
       <c r="G50" s="9" t="inlineStr"/>
-      <c r="H50" s="9" t="inlineStr">
+      <c r="H50" s="9" t="inlineStr"/>
+      <c r="I50" s="9" t="inlineStr"/>
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>←</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr"/>
-      <c r="J50" s="9" t="inlineStr"/>
       <c r="K50" s="9" t="inlineStr"/>
-      <c r="L50" s="9" t="inlineStr">
+      <c r="L50" s="9" t="inlineStr"/>
+      <c r="M50" s="9" t="inlineStr"/>
+      <c r="N50" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -3003,13 +3109,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr"/>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -3032,6 +3138,18 @@
         <is>
           <t>pos 29
 &amp;none</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -3056,6 +3174,12 @@
       <c r="J52" s="9" t="inlineStr"/>
       <c r="K52" s="9" t="inlineStr"/>
       <c r="L52" s="9" t="inlineStr"/>
+      <c r="M52" s="9" t="inlineStr"/>
+      <c r="N52" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
@@ -3065,41 +3189,31 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>pos 30
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
           <t>pos 32
 &amp;trans</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;trans</t>
         </is>
       </c>
+      <c r="D53" s="7" t="inlineStr"/>
+      <c r="E53" s="7" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr"/>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
+      <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -3112,13 +3226,15 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="K53" s="7" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L53" s="7" t="inlineStr">
+      <c r="N53" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -3131,22 +3247,18 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B54" s="9" t="inlineStr"/>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>▽</t>
+        </is>
+      </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>RShift</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="D54" s="9" t="inlineStr"/>
+      <c r="E54" s="9" t="inlineStr"/>
       <c r="F54" s="9" t="inlineStr"/>
       <c r="G54" s="9" t="inlineStr"/>
       <c r="H54" s="9" t="inlineStr"/>
@@ -3154,6 +3266,8 @@
       <c r="J54" s="9" t="inlineStr"/>
       <c r="K54" s="9" t="inlineStr"/>
       <c r="L54" s="9" t="inlineStr"/>
+      <c r="M54" s="9" t="inlineStr"/>
+      <c r="N54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -3171,7 +3285,9 @@
       <c r="I55" s="4" t="n"/>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
-      <c r="L55" s="5" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="5" t="n"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
@@ -3210,31 +3326,33 @@
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr"/>
-      <c r="H56" s="7" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr"/>
+      <c r="J56" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;macro_vim_visual_y</t>
         </is>
       </c>
-      <c r="I56" s="7" t="inlineStr">
+      <c r="K56" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="J56" s="7" t="inlineStr">
+      <c r="L56" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="K56" s="7" t="inlineStr">
+      <c r="M56" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="L56" s="7" t="inlineStr">
+      <c r="N56" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;macro_vim_visual_p</t>
@@ -3261,7 +3379,9 @@
       <c r="E57" s="9" t="inlineStr"/>
       <c r="F57" s="9" t="inlineStr"/>
       <c r="G57" s="9" t="inlineStr"/>
-      <c r="H57" s="10" t="inlineStr">
+      <c r="H57" s="9" t="inlineStr"/>
+      <c r="I57" s="9" t="inlineStr"/>
+      <c r="J57" s="10" t="inlineStr">
         <is>
           <t>LShift
 ▸ RShift
@@ -3270,10 +3390,10 @@
 ▸ ⇒BASE_QWERTY</t>
         </is>
       </c>
-      <c r="I57" s="9" t="inlineStr"/>
-      <c r="J57" s="9" t="inlineStr"/>
       <c r="K57" s="9" t="inlineStr"/>
-      <c r="L57" s="10" t="inlineStr">
+      <c r="L57" s="9" t="inlineStr"/>
+      <c r="M57" s="9" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>LShift
 ▸ RShift
@@ -3319,31 +3439,33 @@
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr"/>
-      <c r="H58" s="7" t="inlineStr">
+      <c r="H58" s="7" t="inlineStr"/>
+      <c r="I58" s="7" t="inlineStr"/>
+      <c r="J58" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LS(LEFT)</t>
         </is>
       </c>
-      <c r="I58" s="7" t="inlineStr">
+      <c r="K58" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp LS(DOWN)</t>
         </is>
       </c>
-      <c r="J58" s="7" t="inlineStr">
+      <c r="L58" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp LS(UP)</t>
         </is>
       </c>
-      <c r="K58" s="7" t="inlineStr">
+      <c r="M58" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp LS(RIGHT)</t>
         </is>
       </c>
-      <c r="L58" s="7" t="inlineStr">
+      <c r="N58" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -3373,27 +3495,29 @@
       <c r="E59" s="9" t="inlineStr"/>
       <c r="F59" s="9" t="inlineStr"/>
       <c r="G59" s="9" t="inlineStr"/>
-      <c r="H59" s="9" t="inlineStr">
+      <c r="H59" s="9" t="inlineStr"/>
+      <c r="I59" s="9" t="inlineStr"/>
+      <c r="J59" s="9" t="inlineStr">
         <is>
           <t>⇧←</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
+      <c r="K59" s="9" t="inlineStr">
         <is>
           <t>⇧↓</t>
         </is>
       </c>
-      <c r="J59" s="9" t="inlineStr">
+      <c r="L59" s="9" t="inlineStr">
         <is>
           <t>⇧↑</t>
         </is>
       </c>
-      <c r="K59" s="9" t="inlineStr">
+      <c r="M59" s="9" t="inlineStr">
         <is>
           <t>⇧→</t>
         </is>
       </c>
-      <c r="L59" s="9" t="inlineStr">
+      <c r="N59" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -3423,16 +3547,8 @@
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr"/>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="H60" s="9" t="inlineStr"/>
+      <c r="I60" s="9" t="inlineStr"/>
       <c r="J60" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -3444,6 +3560,16 @@
         </is>
       </c>
       <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N60" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -3473,16 +3599,8 @@
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr"/>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="H61" s="9" t="inlineStr"/>
+      <c r="I61" s="9" t="inlineStr"/>
       <c r="J61" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -3494,6 +3612,16 @@
         </is>
       </c>
       <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N61" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -3535,13 +3663,13 @@
 &amp;kp LS(LC(LEFT))</t>
         </is>
       </c>
-      <c r="G62" s="7" t="inlineStr"/>
-      <c r="H62" s="7" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -3564,6 +3692,18 @@
         <is>
           <t>pos 29
 &amp;none</t>
+        </is>
+      </c>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N62" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -3610,6 +3750,12 @@
       </c>
       <c r="K63" s="9" t="inlineStr"/>
       <c r="L63" s="9" t="inlineStr"/>
+      <c r="M63" s="9" t="inlineStr"/>
+      <c r="N63" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
@@ -3619,41 +3765,31 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>pos 30
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>pos 31
-&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
           <t>pos 33
 &amp;none</t>
         </is>
       </c>
+      <c r="D64" s="7" t="inlineStr"/>
+      <c r="E64" s="7" t="inlineStr"/>
       <c r="F64" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G64" s="7" t="inlineStr"/>
-      <c r="H64" s="7" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;mo VIM_VISUAL_SYM</t>
         </is>
       </c>
+      <c r="H64" s="7" t="inlineStr"/>
       <c r="I64" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -3666,13 +3802,15 @@
 &amp;mo VIM_VISUAL_SYM</t>
         </is>
       </c>
-      <c r="K64" s="7" t="inlineStr">
+      <c r="K64" s="7" t="inlineStr"/>
+      <c r="L64" s="7" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L64" s="7" t="inlineStr">
+      <c r="N64" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -3686,20 +3824,16 @@
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr"/>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>RShift</t>
-        </is>
-      </c>
+      <c r="C65" s="9" t="inlineStr"/>
       <c r="D65" s="9" t="inlineStr"/>
       <c r="E65" s="9" t="inlineStr"/>
       <c r="F65" s="9" t="inlineStr"/>
-      <c r="G65" s="9" t="inlineStr"/>
-      <c r="H65" s="9" t="inlineStr">
+      <c r="G65" s="9" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
+      <c r="H65" s="9" t="inlineStr"/>
       <c r="I65" s="9" t="inlineStr"/>
       <c r="J65" s="9" t="inlineStr">
         <is>
@@ -3708,6 +3842,8 @@
       </c>
       <c r="K65" s="9" t="inlineStr"/>
       <c r="L65" s="9" t="inlineStr"/>
+      <c r="M65" s="9" t="inlineStr"/>
+      <c r="N65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -3725,7 +3861,9 @@
       <c r="I66" s="4" t="n"/>
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="4" t="n"/>
-      <c r="L66" s="5" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="n"/>
+      <c r="N66" s="5" t="n"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
@@ -3764,31 +3902,33 @@
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr"/>
-      <c r="H67" s="7" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr"/>
+      <c r="I67" s="7" t="inlineStr"/>
+      <c r="J67" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;mm_vim_visual_shift_6</t>
         </is>
       </c>
-      <c r="I67" s="7" t="inlineStr">
+      <c r="K67" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="J67" s="7" t="inlineStr">
+      <c r="L67" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="K67" s="7" t="inlineStr">
+      <c r="M67" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="L67" s="7" t="inlineStr">
+      <c r="N67" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp LS(HOME)</t>
@@ -3811,7 +3951,9 @@
       <c r="I68" s="9" t="inlineStr"/>
       <c r="J68" s="9" t="inlineStr"/>
       <c r="K68" s="9" t="inlineStr"/>
-      <c r="L68" s="9" t="inlineStr">
+      <c r="L68" s="9" t="inlineStr"/>
+      <c r="M68" s="9" t="inlineStr"/>
+      <c r="N68" s="9" t="inlineStr">
         <is>
           <t>⇧HOME</t>
         </is>
@@ -3833,15 +3975,17 @@
       </c>
       <c r="F69" s="9" t="inlineStr"/>
       <c r="G69" s="9" t="inlineStr"/>
-      <c r="H69" s="9" t="inlineStr">
+      <c r="H69" s="9" t="inlineStr"/>
+      <c r="I69" s="9" t="inlineStr"/>
+      <c r="J69" s="9" t="inlineStr">
         <is>
           <t>⇧HOME</t>
         </is>
       </c>
-      <c r="I69" s="9" t="inlineStr"/>
-      <c r="J69" s="9" t="inlineStr"/>
       <c r="K69" s="9" t="inlineStr"/>
-      <c r="L69" s="9" t="inlineStr">
+      <c r="L69" s="9" t="inlineStr"/>
+      <c r="M69" s="9" t="inlineStr"/>
+      <c r="N69" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -3884,31 +4028,33 @@
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr"/>
-      <c r="H70" s="7" t="inlineStr">
+      <c r="H70" s="7" t="inlineStr"/>
+      <c r="I70" s="7" t="inlineStr"/>
+      <c r="J70" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LS(LEFT)</t>
         </is>
       </c>
-      <c r="I70" s="7" t="inlineStr">
+      <c r="K70" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="J70" s="7" t="inlineStr">
+      <c r="L70" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="K70" s="7" t="inlineStr">
+      <c r="M70" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="L70" s="7" t="inlineStr">
+      <c r="N70" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -3931,15 +4077,17 @@
       <c r="E71" s="9" t="inlineStr"/>
       <c r="F71" s="9" t="inlineStr"/>
       <c r="G71" s="9" t="inlineStr"/>
-      <c r="H71" s="9" t="inlineStr">
+      <c r="H71" s="9" t="inlineStr"/>
+      <c r="I71" s="9" t="inlineStr"/>
+      <c r="J71" s="9" t="inlineStr">
         <is>
           <t>⇧←</t>
         </is>
       </c>
-      <c r="I71" s="9" t="inlineStr"/>
-      <c r="J71" s="9" t="inlineStr"/>
       <c r="K71" s="9" t="inlineStr"/>
-      <c r="L71" s="9" t="inlineStr">
+      <c r="L71" s="9" t="inlineStr"/>
+      <c r="M71" s="9" t="inlineStr"/>
+      <c r="N71" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -3981,13 +4129,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G72" s="7" t="inlineStr"/>
-      <c r="H72" s="7" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H72" s="7" t="inlineStr"/>
       <c r="I72" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -4010,6 +4158,18 @@
         <is>
           <t>pos 29
 &amp;none</t>
+        </is>
+      </c>
+      <c r="M72" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N72" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -4034,6 +4194,12 @@
       <c r="J73" s="9" t="inlineStr"/>
       <c r="K73" s="9" t="inlineStr"/>
       <c r="L73" s="9" t="inlineStr"/>
+      <c r="M73" s="9" t="inlineStr"/>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
@@ -4043,41 +4209,31 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>pos 30
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>pos 31
-&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
           <t>pos 33
 &amp;none</t>
         </is>
       </c>
+      <c r="D74" s="7" t="inlineStr"/>
+      <c r="E74" s="7" t="inlineStr"/>
       <c r="F74" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr"/>
-      <c r="H74" s="7" t="inlineStr">
+      <c r="G74" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
+      <c r="H74" s="7" t="inlineStr"/>
       <c r="I74" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -4090,13 +4246,15 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="K74" s="7" t="inlineStr">
+      <c r="K74" s="7" t="inlineStr"/>
+      <c r="L74" s="7" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L74" s="7" t="inlineStr">
+      <c r="N74" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -4110,11 +4268,7 @@
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr"/>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>RShift</t>
-        </is>
-      </c>
+      <c r="C75" s="9" t="inlineStr"/>
       <c r="D75" s="9" t="inlineStr"/>
       <c r="E75" s="9" t="inlineStr"/>
       <c r="F75" s="9" t="inlineStr"/>
@@ -4124,6 +4278,8 @@
       <c r="J75" s="9" t="inlineStr"/>
       <c r="K75" s="9" t="inlineStr"/>
       <c r="L75" s="9" t="inlineStr"/>
+      <c r="M75" s="9" t="inlineStr"/>
+      <c r="N75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -4141,7 +4297,9 @@
       <c r="I76" s="4" t="n"/>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
-      <c r="L76" s="5" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="5" t="n"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
@@ -4180,31 +4338,33 @@
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr"/>
-      <c r="H77" s="7" t="inlineStr">
+      <c r="H77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp F6</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
+      <c r="K77" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp F7</t>
         </is>
       </c>
-      <c r="J77" s="7" t="inlineStr">
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp F8</t>
         </is>
       </c>
-      <c r="K77" s="7" t="inlineStr">
+      <c r="M77" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp F9</t>
         </is>
       </c>
-      <c r="L77" s="7" t="inlineStr">
+      <c r="N77" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp F10</t>
@@ -4243,27 +4403,29 @@
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr"/>
-      <c r="H78" s="9" t="inlineStr">
+      <c r="H78" s="9" t="inlineStr"/>
+      <c r="I78" s="9" t="inlineStr"/>
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>F6</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
+      <c r="K78" s="9" t="inlineStr">
         <is>
           <t>F7</t>
         </is>
       </c>
-      <c r="J78" s="9" t="inlineStr">
+      <c r="L78" s="9" t="inlineStr">
         <is>
           <t>F8</t>
         </is>
       </c>
-      <c r="K78" s="9" t="inlineStr">
+      <c r="M78" s="9" t="inlineStr">
         <is>
           <t>F9</t>
         </is>
       </c>
-      <c r="L78" s="9" t="inlineStr">
+      <c r="N78" s="9" t="inlineStr">
         <is>
           <t>F10</t>
         </is>
@@ -4306,31 +4468,33 @@
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
-      <c r="H79" s="7" t="inlineStr">
+      <c r="H79" s="7" t="inlineStr"/>
+      <c r="I79" s="7" t="inlineStr"/>
+      <c r="J79" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
+      <c r="K79" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="J79" s="7" t="inlineStr">
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="K79" s="7" t="inlineStr">
+      <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="L79" s="7" t="inlineStr">
+      <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
@@ -4356,12 +4520,14 @@
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
       <c r="J80" s="9" t="inlineStr"/>
-      <c r="K80" s="9" t="inlineStr">
+      <c r="K80" s="9" t="inlineStr"/>
+      <c r="L80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr">
         <is>
           <t>リセット</t>
         </is>
       </c>
-      <c r="L80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr"/>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -4399,13 +4565,13 @@
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H81" s="7" t="inlineStr"/>
       <c r="I81" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -4427,6 +4593,18 @@
       <c r="L81" s="7" t="inlineStr">
         <is>
           <t>pos 29
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N81" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
@@ -4456,6 +4634,8 @@
       </c>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
+      <c r="M82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -4465,41 +4645,31 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>pos 30
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
           <t>pos 33
 &amp;none</t>
         </is>
       </c>
+      <c r="D83" s="7" t="inlineStr"/>
+      <c r="E83" s="7" t="inlineStr"/>
       <c r="F83" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G83" s="7" t="inlineStr"/>
-      <c r="H83" s="7" t="inlineStr">
+      <c r="G83" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
+      <c r="H83" s="7" t="inlineStr"/>
       <c r="I83" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -4512,13 +4682,15 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="K83" s="7" t="inlineStr">
+      <c r="K83" s="7" t="inlineStr"/>
+      <c r="L83" s="7" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L83" s="7" t="inlineStr">
+      <c r="N83" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -4542,6 +4714,8 @@
       <c r="J84" s="9" t="inlineStr"/>
       <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr"/>
+      <c r="M84" s="9" t="inlineStr"/>
+      <c r="N84" s="9" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -4559,7 +4733,9 @@
       <c r="I85" s="4" t="n"/>
       <c r="J85" s="4" t="n"/>
       <c r="K85" s="4" t="n"/>
-      <c r="L85" s="5" t="n"/>
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="4" t="n"/>
+      <c r="N85" s="5" t="n"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
@@ -4598,31 +4774,33 @@
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr"/>
-      <c r="H86" s="7" t="inlineStr">
+      <c r="H86" s="7" t="inlineStr"/>
+      <c r="I86" s="7" t="inlineStr"/>
+      <c r="J86" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;none</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
+      <c r="K86" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;out OUT_USB</t>
         </is>
       </c>
-      <c r="J86" s="7" t="inlineStr">
+      <c r="L86" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="K86" s="7" t="inlineStr">
+      <c r="M86" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="L86" s="7" t="inlineStr">
+      <c r="N86" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -4662,14 +4840,16 @@
       </c>
       <c r="G87" s="9" t="inlineStr"/>
       <c r="H87" s="9" t="inlineStr"/>
-      <c r="I87" s="9" t="inlineStr">
+      <c r="I87" s="9" t="inlineStr"/>
+      <c r="J87" s="9" t="inlineStr"/>
+      <c r="K87" s="9" t="inlineStr">
         <is>
           <t>USB出力</t>
         </is>
       </c>
-      <c r="J87" s="9" t="inlineStr"/>
-      <c r="K87" s="9" t="inlineStr"/>
       <c r="L87" s="9" t="inlineStr"/>
+      <c r="M87" s="9" t="inlineStr"/>
+      <c r="N87" s="9" t="inlineStr"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
@@ -4708,31 +4888,33 @@
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr"/>
-      <c r="H88" s="7" t="inlineStr">
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr"/>
+      <c r="J88" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
+      <c r="K88" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="J88" s="7" t="inlineStr">
+      <c r="L88" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="K88" s="7" t="inlineStr">
+      <c r="M88" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="L88" s="7" t="inlineStr">
+      <c r="N88" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
@@ -4760,6 +4942,8 @@
       <c r="J89" s="9" t="inlineStr"/>
       <c r="K89" s="9" t="inlineStr"/>
       <c r="L89" s="9" t="inlineStr"/>
+      <c r="M89" s="9" t="inlineStr"/>
+      <c r="N89" s="9" t="inlineStr"/>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
@@ -4797,13 +4981,13 @@
 &amp;out OUT_BLE</t>
         </is>
       </c>
-      <c r="G90" s="7" t="inlineStr"/>
-      <c r="H90" s="7" t="inlineStr">
+      <c r="G90" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H90" s="7" t="inlineStr"/>
       <c r="I90" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -4825,6 +5009,18 @@
       <c r="L90" s="7" t="inlineStr">
         <is>
           <t>pos 29
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M90" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N90" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
@@ -4854,6 +5050,8 @@
       <c r="J91" s="9" t="inlineStr"/>
       <c r="K91" s="9" t="inlineStr"/>
       <c r="L91" s="9" t="inlineStr"/>
+      <c r="M91" s="9" t="inlineStr"/>
+      <c r="N91" s="9" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
@@ -4863,41 +5061,31 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>pos 30
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
           <t>pos 33
 &amp;none</t>
         </is>
       </c>
+      <c r="D92" s="7" t="inlineStr"/>
+      <c r="E92" s="7" t="inlineStr"/>
       <c r="F92" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G92" s="7" t="inlineStr"/>
-      <c r="H92" s="7" t="inlineStr">
+      <c r="G92" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
+      <c r="H92" s="7" t="inlineStr"/>
       <c r="I92" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -4910,13 +5098,15 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="K92" s="7" t="inlineStr">
+      <c r="K92" s="7" t="inlineStr"/>
+      <c r="L92" s="7" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L92" s="7" t="inlineStr">
+      <c r="N92" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -4940,6 +5130,8 @@
       <c r="J93" s="9" t="inlineStr"/>
       <c r="K93" s="9" t="inlineStr"/>
       <c r="L93" s="9" t="inlineStr"/>
+      <c r="M93" s="9" t="inlineStr"/>
+      <c r="N93" s="9" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -4957,7 +5149,9 @@
       <c r="I94" s="4" t="n"/>
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="n"/>
-      <c r="L94" s="5" t="n"/>
+      <c r="L94" s="4" t="n"/>
+      <c r="M94" s="4" t="n"/>
+      <c r="N94" s="5" t="n"/>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
@@ -4996,31 +5190,33 @@
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr"/>
-      <c r="H95" s="7" t="inlineStr">
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;none</t>
         </is>
       </c>
-      <c r="I95" s="7" t="inlineStr">
+      <c r="K95" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="J95" s="7" t="inlineStr">
+      <c r="L95" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="K95" s="7" t="inlineStr">
+      <c r="M95" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="L95" s="7" t="inlineStr">
+      <c r="N95" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -5044,6 +5240,8 @@
       <c r="J96" s="9" t="inlineStr"/>
       <c r="K96" s="9" t="inlineStr"/>
       <c r="L96" s="9" t="inlineStr"/>
+      <c r="M96" s="9" t="inlineStr"/>
+      <c r="N96" s="9" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
@@ -5082,31 +5280,33 @@
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr"/>
-      <c r="H97" s="7" t="inlineStr">
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr"/>
+      <c r="J97" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="I97" s="7" t="inlineStr">
+      <c r="K97" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="J97" s="7" t="inlineStr">
+      <c r="L97" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
-      <c r="K97" s="7" t="inlineStr">
+      <c r="M97" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="L97" s="7" t="inlineStr">
+      <c r="N97" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;trans</t>
@@ -5135,14 +5335,16 @@
       <c r="G98" s="9" t="inlineStr"/>
       <c r="H98" s="9" t="inlineStr"/>
       <c r="I98" s="9" t="inlineStr"/>
-      <c r="J98" s="9" t="inlineStr">
-        <is>
-          <t>L9</t>
-        </is>
-      </c>
+      <c r="J98" s="9" t="inlineStr"/>
       <c r="K98" s="9" t="inlineStr"/>
       <c r="L98" s="9" t="inlineStr">
         <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="M98" s="9" t="inlineStr"/>
+      <c r="N98" s="9" t="inlineStr">
+        <is>
           <t>▽</t>
         </is>
       </c>
@@ -5183,13 +5385,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G99" s="7" t="inlineStr"/>
-      <c r="H99" s="7" t="inlineStr">
+      <c r="G99" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -5212,6 +5414,18 @@
         <is>
           <t>pos 29
 &amp;none</t>
+        </is>
+      </c>
+      <c r="M99" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N99" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;trans</t>
         </is>
       </c>
     </row>
@@ -5236,6 +5450,12 @@
       <c r="J100" s="9" t="inlineStr"/>
       <c r="K100" s="9" t="inlineStr"/>
       <c r="L100" s="9" t="inlineStr"/>
+      <c r="M100" s="9" t="inlineStr"/>
+      <c r="N100" s="9" t="inlineStr">
+        <is>
+          <t>▽</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
@@ -5245,41 +5465,31 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>pos 30
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;trans</t>
-        </is>
-      </c>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
           <t>pos 32
 &amp;trans</t>
         </is>
       </c>
-      <c r="E101" s="7" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;trans</t>
         </is>
       </c>
+      <c r="D101" s="7" t="inlineStr"/>
+      <c r="E101" s="7" t="inlineStr"/>
       <c r="F101" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G101" s="7" t="inlineStr"/>
-      <c r="H101" s="7" t="inlineStr">
+      <c r="G101" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
+      <c r="H101" s="7" t="inlineStr"/>
       <c r="I101" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -5292,13 +5502,15 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="K101" s="7" t="inlineStr">
+      <c r="K101" s="7" t="inlineStr"/>
+      <c r="L101" s="7" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L101" s="7" t="inlineStr">
+      <c r="N101" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -5311,22 +5523,18 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B102" s="9" t="inlineStr"/>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>▽</t>
+        </is>
+      </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
-      <c r="E102" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="D102" s="9" t="inlineStr"/>
+      <c r="E102" s="9" t="inlineStr"/>
       <c r="F102" s="9" t="inlineStr"/>
       <c r="G102" s="9" t="inlineStr"/>
       <c r="H102" s="9" t="inlineStr"/>
@@ -5334,6 +5542,8 @@
       <c r="J102" s="9" t="inlineStr"/>
       <c r="K102" s="9" t="inlineStr"/>
       <c r="L102" s="9" t="inlineStr"/>
+      <c r="M102" s="9" t="inlineStr"/>
+      <c r="N102" s="9" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -5351,7 +5561,9 @@
       <c r="I103" s="4" t="n"/>
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="4" t="n"/>
-      <c r="L103" s="5" t="n"/>
+      <c r="L103" s="4" t="n"/>
+      <c r="M103" s="4" t="n"/>
+      <c r="N103" s="5" t="n"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
@@ -5390,31 +5602,33 @@
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr"/>
-      <c r="H104" s="7" t="inlineStr">
+      <c r="H104" s="7" t="inlineStr"/>
+      <c r="I104" s="7" t="inlineStr"/>
+      <c r="J104" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;none</t>
         </is>
       </c>
-      <c r="I104" s="7" t="inlineStr">
+      <c r="K104" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="J104" s="7" t="inlineStr">
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="K104" s="7" t="inlineStr">
+      <c r="M104" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="L104" s="7" t="inlineStr">
+      <c r="N104" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -5438,6 +5652,8 @@
       <c r="J105" s="9" t="inlineStr"/>
       <c r="K105" s="9" t="inlineStr"/>
       <c r="L105" s="9" t="inlineStr"/>
+      <c r="M105" s="9" t="inlineStr"/>
+      <c r="N105" s="9" t="inlineStr"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
@@ -5476,31 +5692,33 @@
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr"/>
-      <c r="H106" s="7" t="inlineStr">
+      <c r="H106" s="7" t="inlineStr"/>
+      <c r="I106" s="7" t="inlineStr"/>
+      <c r="J106" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="I106" s="7" t="inlineStr">
+      <c r="K106" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;mkp MB1</t>
         </is>
       </c>
-      <c r="J106" s="7" t="inlineStr">
+      <c r="L106" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="K106" s="7" t="inlineStr">
+      <c r="M106" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;mkp MB2</t>
         </is>
       </c>
-      <c r="L106" s="7" t="inlineStr">
+      <c r="N106" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -5532,18 +5750,20 @@
       <c r="F107" s="9" t="inlineStr"/>
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
-      <c r="I107" s="9" t="inlineStr">
-        <is>
-          <t>🖱左</t>
-        </is>
-      </c>
+      <c r="I107" s="9" t="inlineStr"/>
       <c r="J107" s="9" t="inlineStr"/>
       <c r="K107" s="9" t="inlineStr">
         <is>
+          <t>🖱左</t>
+        </is>
+      </c>
+      <c r="L107" s="9" t="inlineStr"/>
+      <c r="M107" s="9" t="inlineStr">
+        <is>
           <t>🖱右</t>
         </is>
       </c>
-      <c r="L107" s="9" t="inlineStr">
+      <c r="N107" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -5585,13 +5805,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G108" s="7" t="inlineStr"/>
-      <c r="H108" s="7" t="inlineStr">
+      <c r="G108" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H108" s="7" t="inlineStr"/>
       <c r="I108" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -5614,6 +5834,18 @@
         <is>
           <t>pos 29
 &amp;none</t>
+        </is>
+      </c>
+      <c r="M108" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;mkp MB5</t>
+        </is>
+      </c>
+      <c r="N108" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -5650,6 +5882,16 @@
         </is>
       </c>
       <c r="L109" s="9" t="inlineStr"/>
+      <c r="M109" s="9" t="inlineStr">
+        <is>
+          <t>🖱進</t>
+        </is>
+      </c>
+      <c r="N109" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -5659,41 +5901,31 @@
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>pos 30
-&amp;mkp MB5</t>
-        </is>
-      </c>
-      <c r="C110" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="inlineStr">
-        <is>
           <t>pos 32
 &amp;kp LEFT_WIN</t>
         </is>
       </c>
-      <c r="E110" s="7" t="inlineStr">
+      <c r="C110" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;kp LEFT_ALT</t>
         </is>
       </c>
+      <c r="D110" s="7" t="inlineStr"/>
+      <c r="E110" s="7" t="inlineStr"/>
       <c r="F110" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G110" s="7" t="inlineStr"/>
-      <c r="H110" s="7" t="inlineStr">
+      <c r="G110" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
+      <c r="H110" s="7" t="inlineStr"/>
       <c r="I110" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -5706,13 +5938,15 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="K110" s="7" t="inlineStr">
+      <c r="K110" s="7" t="inlineStr"/>
+      <c r="L110" s="7" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L110" s="7" t="inlineStr">
+      <c r="N110" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -5727,24 +5961,16 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>🖱進</t>
+          <t>LWin</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>RShift</t>
-        </is>
-      </c>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>LWin</t>
-        </is>
-      </c>
-      <c r="E111" s="9" t="inlineStr">
-        <is>
           <t>LAlt</t>
         </is>
       </c>
+      <c r="D111" s="9" t="inlineStr"/>
+      <c r="E111" s="9" t="inlineStr"/>
       <c r="F111" s="9" t="inlineStr"/>
       <c r="G111" s="9" t="inlineStr"/>
       <c r="H111" s="9" t="inlineStr"/>
@@ -5752,19 +5978,21 @@
       <c r="J111" s="9" t="inlineStr"/>
       <c r="K111" s="9" t="inlineStr"/>
       <c r="L111" s="9" t="inlineStr"/>
+      <c r="M111" s="9" t="inlineStr"/>
+      <c r="N111" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A16:L16"/>
-    <mergeCell ref="A76:L76"/>
-    <mergeCell ref="A85:L85"/>
-    <mergeCell ref="A45:L45"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A94:L94"/>
-    <mergeCell ref="A103:L103"/>
-    <mergeCell ref="A66:L66"/>
-    <mergeCell ref="A55:L55"/>
-    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A55:N55"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A45:N45"/>
+    <mergeCell ref="A16:N16"/>
+    <mergeCell ref="A76:N76"/>
+    <mergeCell ref="A85:N85"/>
+    <mergeCell ref="A28:N28"/>
+    <mergeCell ref="A103:N103"/>
+    <mergeCell ref="A66:N66"/>
+    <mergeCell ref="A94:N94"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5776,7 +6004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:N111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5785,12 +6013,14 @@
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="3" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5831,12 +6061,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -5855,6 +6085,16 @@
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>10</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -5874,7 +6114,9 @@
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
-      <c r="L4" s="5" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="5" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -5913,31 +6155,33 @@
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp Y</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp U</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp I</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp O</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp P</t>
@@ -5976,27 +6220,29 @@
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>&amp;kp Y</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>&amp;kp U</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>&amp;kp I</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>&amp;kp O</t>
         </is>
       </c>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>&amp;kp P</t>
         </is>
@@ -6039,31 +6285,33 @@
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp H</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp J</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp K</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp L</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;mt RCTRL MINUS</t>
@@ -6102,27 +6350,29 @@
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>&amp;kp H</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>&amp;kp J</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>&amp;kp K</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>&amp;kp L</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>&amp;mt RCTRL MINUS</t>
         </is>
@@ -6160,16 +6410,8 @@
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="H9" s="9" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr"/>
       <c r="J9" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -6181,6 +6423,16 @@
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>&amp;mt RCTRL MINUS</t>
         </is>
@@ -6222,13 +6474,13 @@
 &amp;kp B</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;mo BLUETOOTH</t>
         </is>
       </c>
+      <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -6253,6 +6505,18 @@
 &amp;kp COMMA</t>
         </is>
       </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;kp PERIOD</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;mt RIGHT_SHIFT SLASH</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -6285,12 +6549,12 @@
           <t>&amp;kp B</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr"/>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>&amp;mo BLUETOOTH</t>
         </is>
       </c>
+      <c r="H11" s="9" t="inlineStr"/>
       <c r="I11" s="9" t="inlineStr">
         <is>
           <t>&amp;mo BLUETOOTH</t>
@@ -6309,6 +6573,16 @@
       <c r="L11" s="9" t="inlineStr">
         <is>
           <t>&amp;kp COMMA</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PERIOD</t>
+        </is>
+      </c>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mt RIGHT_SHIFT SLASH</t>
         </is>
       </c>
     </row>
@@ -6343,12 +6617,12 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr"/>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr"/>
       <c r="I12" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -6367,6 +6641,16 @@
       <c r="L12" s="9" t="inlineStr">
         <is>
           <t>〃</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mt RIGHT_SHIFT SLASH</t>
         </is>
       </c>
     </row>
@@ -6378,41 +6662,31 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>pos 30
-&amp;kp PERIOD</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;mt RIGHT_SHIFT SLASH</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
           <t>pos 32
 &amp;kp LEFT_WIN</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;kp LEFT_ALT</t>
         </is>
       </c>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;mo NUM_SYMBOL</t>
         </is>
       </c>
+      <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -6425,13 +6699,15 @@
 &amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;mo FUNCTION</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;mo FUNCTION</t>
@@ -6446,35 +6722,27 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp PERIOD</t>
+          <t>&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>&amp;mt RIGHT_SHIFT SLASH</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LEFT_WIN</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
           <t>&amp;kp LEFT_ALT</t>
         </is>
       </c>
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="9" t="inlineStr"/>
       <c r="F14" s="9" t="inlineStr">
         <is>
           <t>&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr"/>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>&amp;mo NUM_SYMBOL</t>
         </is>
       </c>
+      <c r="H14" s="9" t="inlineStr"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
           <t>&amp;mo VIM_NORMAL_BASE</t>
@@ -6485,12 +6753,14 @@
           <t>&amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr"/>
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>&amp;mo FUNCTION</t>
         </is>
       </c>
-      <c r="L14" s="9" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>&amp;mo FUNCTION</t>
         </is>
@@ -6509,30 +6779,22 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>&amp;mt RIGHT_SHIFT SLASH</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
       <c r="F15" s="9" t="inlineStr">
         <is>
           <t>&amp;lt VIM_NORMAL_BASE SPACE</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr"/>
       <c r="I15" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -6543,12 +6805,14 @@
           <t>&amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr"/>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -6570,7 +6834,9 @@
       <c r="I16" s="4" t="n"/>
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
-      <c r="L16" s="5" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="5" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -6609,31 +6875,33 @@
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp N6</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp N7</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp N8</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp N9</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="N17" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp N0</t>
@@ -6672,27 +6940,29 @@
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr"/>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr"/>
+      <c r="I18" s="9" t="inlineStr"/>
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>&amp;kp N6</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>&amp;kp N7</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="L18" s="9" t="inlineStr">
         <is>
           <t>&amp;kp N8</t>
         </is>
       </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="M18" s="9" t="inlineStr">
         <is>
           <t>&amp;kp N9</t>
         </is>
       </c>
-      <c r="L18" s="9" t="inlineStr">
+      <c r="N18" s="9" t="inlineStr">
         <is>
           <t>&amp;kp N0</t>
         </is>
@@ -6735,31 +7005,33 @@
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp BACKSPACE</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp SEMICOLON</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp SINGLE_QUOTE</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp BACKSLASH</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="N19" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;trans</t>
@@ -6798,27 +7070,29 @@
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr"/>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>&amp;kp BACKSPACE</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>&amp;kp SEMICOLON</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>&amp;kp SINGLE_QUOTE</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>&amp;kp BACKSLASH</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr">
+      <c r="N20" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -6856,16 +7130,8 @@
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr"/>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="H21" s="9" t="inlineStr"/>
+      <c r="I21" s="9" t="inlineStr"/>
       <c r="J21" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -6877,6 +7143,16 @@
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -6918,13 +7194,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -6946,6 +7222,18 @@
       <c r="L22" s="7" t="inlineStr">
         <is>
           <t>pos 29
+&amp;trans</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;trans</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
 &amp;trans</t>
         </is>
       </c>
@@ -6979,6 +7267,16 @@
           <t>▽</t>
         </is>
       </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>▽</t>
+        </is>
+      </c>
+      <c r="N23" s="9" t="inlineStr">
+        <is>
+          <t>▽</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -7009,6 +7307,16 @@
           <t>〃</t>
         </is>
       </c>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -7018,41 +7326,31 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>pos 30
-&amp;trans</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;trans</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
           <t>pos 32
 &amp;trans</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;trans</t>
         </is>
       </c>
+      <c r="D25" s="7" t="inlineStr"/>
+      <c r="E25" s="7" t="inlineStr"/>
       <c r="F25" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;lt VIM_NORMAL_SYM SPACE</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
+      <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -7065,13 +7363,15 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="K25" s="7" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="N25" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -7094,16 +7394,8 @@
           <t>▽</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="D26" s="9" t="inlineStr"/>
+      <c r="E26" s="9" t="inlineStr"/>
       <c r="F26" s="9" t="inlineStr">
         <is>
           <t>&amp;lt VIM_NORMAL_SYM SPACE</t>
@@ -7119,6 +7411,8 @@
       <c r="J26" s="9" t="inlineStr"/>
       <c r="K26" s="9" t="inlineStr"/>
       <c r="L26" s="9" t="inlineStr"/>
+      <c r="M26" s="9" t="inlineStr"/>
+      <c r="N26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -7136,16 +7430,8 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="D27" s="9" t="inlineStr"/>
+      <c r="E27" s="9" t="inlineStr"/>
       <c r="F27" s="9" t="inlineStr">
         <is>
           <t>&amp;lt VIM_NORMAL_SYM SPACE</t>
@@ -7161,6 +7447,8 @@
       <c r="J27" s="9" t="inlineStr"/>
       <c r="K27" s="9" t="inlineStr"/>
       <c r="L27" s="9" t="inlineStr"/>
+      <c r="M27" s="9" t="inlineStr"/>
+      <c r="N27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -7178,7 +7466,9 @@
       <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
-      <c r="L28" s="5" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="5" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
@@ -7217,31 +7507,33 @@
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;mm_vim_y</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;mm_vim_u</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;mm_vim_o</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp LC(V)</t>
@@ -7274,27 +7566,29 @@
       </c>
       <c r="F30" s="9" t="inlineStr"/>
       <c r="G30" s="9" t="inlineStr"/>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H30" s="9" t="inlineStr"/>
+      <c r="I30" s="9" t="inlineStr"/>
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>mm_vim_y[0]
 ▸ td_vim_y[0]
 ▸ &amp;none</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="K30" s="10" t="inlineStr">
         <is>
           <t>mm_vim_u[0]
 ▸ &amp;kp LC(Z)</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr"/>
-      <c r="K30" s="10" t="inlineStr">
+      <c r="L30" s="9" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>mm_vim_o[0]
 ▸ macro_vim_o</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr">
+      <c r="N30" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LC(V)</t>
         </is>
@@ -7320,25 +7614,27 @@
       <c r="E31" s="9" t="inlineStr"/>
       <c r="F31" s="9" t="inlineStr"/>
       <c r="G31" s="9" t="inlineStr"/>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr"/>
+      <c r="I31" s="9" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>mm_vim_y[0]
 ▸ td_vim_y[1]
 ▸ macro_vim_yy</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr"/>
       <c r="K31" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="L31" s="9" t="inlineStr">
+      <c r="L31" s="9" t="inlineStr"/>
+      <c r="M31" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N31" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7364,25 +7660,27 @@
       <c r="E32" s="9" t="inlineStr"/>
       <c r="F32" s="9" t="inlineStr"/>
       <c r="G32" s="9" t="inlineStr"/>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H32" s="9" t="inlineStr"/>
+      <c r="I32" s="9" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>mm_vim_y[1]
 ▸ macro_vim_shift_y</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="J32" s="9" t="inlineStr"/>
-      <c r="K32" s="10" t="inlineStr">
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>mm_vim_o[1]
 ▸ macro_vim_shift_o</t>
         </is>
       </c>
-      <c r="L32" s="9" t="inlineStr">
+      <c r="N32" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7415,19 +7713,21 @@
       <c r="F33" s="9" t="inlineStr"/>
       <c r="G33" s="9" t="inlineStr"/>
       <c r="H33" s="9" t="inlineStr"/>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I33" s="9" t="inlineStr"/>
+      <c r="J33" s="9" t="inlineStr"/>
+      <c r="K33" s="10" t="inlineStr">
         <is>
           <t>mm_vim_u[1]
 ▸ &amp;kp PAGE_UP</t>
         </is>
       </c>
-      <c r="J33" s="9" t="inlineStr"/>
-      <c r="K33" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr"/>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N33" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7470,31 +7770,33 @@
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr"/>
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LEFT</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;mm_vim_j</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp UP_ARROW</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp RIGHT</t>
         </is>
       </c>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="N34" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -7530,28 +7832,30 @@
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr"/>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr"/>
+      <c r="I35" s="9" t="inlineStr"/>
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LEFT</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>mm_vim_j[0]
 ▸ &amp;kp DOWN</t>
         </is>
       </c>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="L35" s="9" t="inlineStr">
         <is>
           <t>&amp;kp UP_ARROW</t>
         </is>
       </c>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="M35" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RIGHT</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr">
+      <c r="N35" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RCTRL</t>
         </is>
@@ -7586,16 +7890,8 @@
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="H36" s="9" t="inlineStr"/>
+      <c r="I36" s="9" t="inlineStr"/>
       <c r="J36" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -7607,6 +7903,16 @@
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M36" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N36" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7639,28 +7945,30 @@
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr"/>
-      <c r="H37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="H37" s="9" t="inlineStr"/>
+      <c r="I37" s="9" t="inlineStr"/>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>mm_vim_j[1]
 ▸ macro_vim_join</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
       <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N37" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7687,16 +7995,8 @@
       <c r="E38" s="9" t="inlineStr"/>
       <c r="F38" s="9" t="inlineStr"/>
       <c r="G38" s="9" t="inlineStr"/>
-      <c r="H38" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="H38" s="9" t="inlineStr"/>
+      <c r="I38" s="9" t="inlineStr"/>
       <c r="J38" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -7708,6 +8008,16 @@
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M38" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N38" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7749,13 +8059,13 @@
 &amp;kp LC(LEFT)</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr"/>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -7778,6 +8088,18 @@
         <is>
           <t>pos 29
 &amp;none</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -7820,6 +8142,12 @@
       </c>
       <c r="K40" s="9" t="inlineStr"/>
       <c r="L40" s="9" t="inlineStr"/>
+      <c r="M40" s="9" t="inlineStr"/>
+      <c r="N40" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
@@ -7859,6 +8187,12 @@
       </c>
       <c r="K41" s="9" t="inlineStr"/>
       <c r="L41" s="9" t="inlineStr"/>
+      <c r="M41" s="9" t="inlineStr"/>
+      <c r="N41" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
@@ -7868,41 +8202,31 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>pos 30
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
           <t>pos 32
 &amp;trans</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;trans</t>
         </is>
       </c>
+      <c r="D42" s="7" t="inlineStr"/>
+      <c r="E42" s="7" t="inlineStr"/>
       <c r="F42" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
+      <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -7915,13 +8239,15 @@
 &amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
-      <c r="K42" s="7" t="inlineStr">
+      <c r="K42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L42" s="7" t="inlineStr">
+      <c r="N42" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -7934,29 +8260,25 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr"/>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>▽</t>
+        </is>
+      </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="D43" s="9" t="inlineStr"/>
+      <c r="E43" s="9" t="inlineStr"/>
       <c r="F43" s="9" t="inlineStr"/>
-      <c r="G43" s="9" t="inlineStr"/>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr">
         <is>
           <t>&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
+      <c r="H43" s="9" t="inlineStr"/>
       <c r="I43" s="9" t="inlineStr"/>
       <c r="J43" s="9" t="inlineStr">
         <is>
@@ -7965,6 +8287,8 @@
       </c>
       <c r="K43" s="9" t="inlineStr"/>
       <c r="L43" s="9" t="inlineStr"/>
+      <c r="M43" s="9" t="inlineStr"/>
+      <c r="N43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -7972,29 +8296,25 @@
           <t>ホールド</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr"/>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr"/>
       <c r="F44" s="9" t="inlineStr"/>
-      <c r="G44" s="9" t="inlineStr"/>
-      <c r="H44" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr"/>
       <c r="I44" s="9" t="inlineStr"/>
       <c r="J44" s="9" t="inlineStr">
         <is>
@@ -8003,6 +8323,8 @@
       </c>
       <c r="K44" s="9" t="inlineStr"/>
       <c r="L44" s="9" t="inlineStr"/>
+      <c r="M44" s="9" t="inlineStr"/>
+      <c r="N44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -8020,7 +8342,9 @@
       <c r="I45" s="4" t="n"/>
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
-      <c r="L45" s="5" t="n"/>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="n"/>
+      <c r="N45" s="5" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
@@ -8059,31 +8383,33 @@
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr"/>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr"/>
+      <c r="I46" s="7" t="inlineStr"/>
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;mm_vim_shift_6</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="K46" s="7" t="inlineStr">
+      <c r="M46" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="L46" s="7" t="inlineStr">
+      <c r="N46" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp HOME</t>
@@ -8107,16 +8433,18 @@
       </c>
       <c r="F47" s="9" t="inlineStr"/>
       <c r="G47" s="9" t="inlineStr"/>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="H47" s="9" t="inlineStr"/>
+      <c r="I47" s="9" t="inlineStr"/>
+      <c r="J47" s="10" t="inlineStr">
         <is>
           <t>mm_vim_shift_6[0]
 ▸ &amp;none</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr"/>
-      <c r="J47" s="9" t="inlineStr"/>
       <c r="K47" s="9" t="inlineStr"/>
-      <c r="L47" s="9" t="inlineStr">
+      <c r="L47" s="9" t="inlineStr"/>
+      <c r="M47" s="9" t="inlineStr"/>
+      <c r="N47" s="9" t="inlineStr">
         <is>
           <t>&amp;kp HOME</t>
         </is>
@@ -8139,16 +8467,18 @@
       </c>
       <c r="F48" s="9" t="inlineStr"/>
       <c r="G48" s="9" t="inlineStr"/>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="H48" s="9" t="inlineStr"/>
+      <c r="I48" s="9" t="inlineStr"/>
+      <c r="J48" s="10" t="inlineStr">
         <is>
           <t>mm_vim_shift_6[1]
 ▸ &amp;kp HOME</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr"/>
-      <c r="J48" s="9" t="inlineStr"/>
       <c r="K48" s="9" t="inlineStr"/>
-      <c r="L48" s="9" t="inlineStr">
+      <c r="L48" s="9" t="inlineStr"/>
+      <c r="M48" s="9" t="inlineStr"/>
+      <c r="N48" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -8191,31 +8521,33 @@
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr"/>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr"/>
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LEFT</t>
         </is>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="K49" s="7" t="inlineStr">
+      <c r="M49" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="L49" s="7" t="inlineStr">
+      <c r="N49" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -8238,15 +8570,17 @@
       <c r="E50" s="9" t="inlineStr"/>
       <c r="F50" s="9" t="inlineStr"/>
       <c r="G50" s="9" t="inlineStr"/>
-      <c r="H50" s="9" t="inlineStr">
+      <c r="H50" s="9" t="inlineStr"/>
+      <c r="I50" s="9" t="inlineStr"/>
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LEFT</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr"/>
-      <c r="J50" s="9" t="inlineStr"/>
       <c r="K50" s="9" t="inlineStr"/>
-      <c r="L50" s="9" t="inlineStr">
+      <c r="L50" s="9" t="inlineStr"/>
+      <c r="M50" s="9" t="inlineStr"/>
+      <c r="N50" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RCTRL</t>
         </is>
@@ -8288,13 +8622,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr"/>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -8317,6 +8651,18 @@
         <is>
           <t>pos 29
 &amp;none</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -8341,6 +8687,12 @@
       <c r="J52" s="9" t="inlineStr"/>
       <c r="K52" s="9" t="inlineStr"/>
       <c r="L52" s="9" t="inlineStr"/>
+      <c r="M52" s="9" t="inlineStr"/>
+      <c r="N52" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
@@ -8350,41 +8702,31 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>pos 30
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
           <t>pos 32
 &amp;trans</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;trans</t>
         </is>
       </c>
+      <c r="D53" s="7" t="inlineStr"/>
+      <c r="E53" s="7" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr"/>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
+      <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -8397,13 +8739,15 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="K53" s="7" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L53" s="7" t="inlineStr">
+      <c r="N53" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -8416,22 +8760,18 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B54" s="9" t="inlineStr"/>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>▽</t>
+        </is>
+      </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="D54" s="9" t="inlineStr"/>
+      <c r="E54" s="9" t="inlineStr"/>
       <c r="F54" s="9" t="inlineStr"/>
       <c r="G54" s="9" t="inlineStr"/>
       <c r="H54" s="9" t="inlineStr"/>
@@ -8439,6 +8779,8 @@
       <c r="J54" s="9" t="inlineStr"/>
       <c r="K54" s="9" t="inlineStr"/>
       <c r="L54" s="9" t="inlineStr"/>
+      <c r="M54" s="9" t="inlineStr"/>
+      <c r="N54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -8456,7 +8798,9 @@
       <c r="I55" s="4" t="n"/>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
-      <c r="L55" s="5" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="5" t="n"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
@@ -8495,31 +8839,33 @@
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr"/>
-      <c r="H56" s="7" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr"/>
+      <c r="J56" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;macro_vim_visual_y</t>
         </is>
       </c>
-      <c r="I56" s="7" t="inlineStr">
+      <c r="K56" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="J56" s="7" t="inlineStr">
+      <c r="L56" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="K56" s="7" t="inlineStr">
+      <c r="M56" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="L56" s="7" t="inlineStr">
+      <c r="N56" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;macro_vim_visual_p</t>
@@ -8546,15 +8892,17 @@
       <c r="E57" s="9" t="inlineStr"/>
       <c r="F57" s="9" t="inlineStr"/>
       <c r="G57" s="9" t="inlineStr"/>
-      <c r="H57" s="9" t="inlineStr">
+      <c r="H57" s="9" t="inlineStr"/>
+      <c r="I57" s="9" t="inlineStr"/>
+      <c r="J57" s="9" t="inlineStr">
         <is>
           <t>macro_vim_visual_y</t>
         </is>
       </c>
-      <c r="I57" s="9" t="inlineStr"/>
-      <c r="J57" s="9" t="inlineStr"/>
       <c r="K57" s="9" t="inlineStr"/>
-      <c r="L57" s="9" t="inlineStr">
+      <c r="L57" s="9" t="inlineStr"/>
+      <c r="M57" s="9" t="inlineStr"/>
+      <c r="N57" s="9" t="inlineStr">
         <is>
           <t>macro_vim_visual_p</t>
         </is>
@@ -8597,31 +8945,33 @@
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr"/>
-      <c r="H58" s="7" t="inlineStr">
+      <c r="H58" s="7" t="inlineStr"/>
+      <c r="I58" s="7" t="inlineStr"/>
+      <c r="J58" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LS(LEFT)</t>
         </is>
       </c>
-      <c r="I58" s="7" t="inlineStr">
+      <c r="K58" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp LS(DOWN)</t>
         </is>
       </c>
-      <c r="J58" s="7" t="inlineStr">
+      <c r="L58" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp LS(UP)</t>
         </is>
       </c>
-      <c r="K58" s="7" t="inlineStr">
+      <c r="M58" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp LS(RIGHT)</t>
         </is>
       </c>
-      <c r="L58" s="7" t="inlineStr">
+      <c r="N58" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -8654,27 +9004,29 @@
         </is>
       </c>
       <c r="G59" s="9" t="inlineStr"/>
-      <c r="H59" s="9" t="inlineStr">
+      <c r="H59" s="9" t="inlineStr"/>
+      <c r="I59" s="9" t="inlineStr"/>
+      <c r="J59" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LS(LEFT)</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
+      <c r="K59" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LS(DOWN)</t>
         </is>
       </c>
-      <c r="J59" s="9" t="inlineStr">
+      <c r="L59" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LS(UP)</t>
         </is>
       </c>
-      <c r="K59" s="9" t="inlineStr">
+      <c r="M59" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LS(RIGHT)</t>
         </is>
       </c>
-      <c r="L59" s="9" t="inlineStr">
+      <c r="N59" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RCTRL</t>
         </is>
@@ -8706,16 +9058,8 @@
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr"/>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="H60" s="9" t="inlineStr"/>
+      <c r="I60" s="9" t="inlineStr"/>
       <c r="J60" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -8727,6 +9071,16 @@
         </is>
       </c>
       <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N60" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -8757,16 +9111,8 @@
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr"/>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="H61" s="9" t="inlineStr"/>
+      <c r="I61" s="9" t="inlineStr"/>
       <c r="J61" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -8778,6 +9124,16 @@
         </is>
       </c>
       <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N61" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -8819,13 +9175,13 @@
 &amp;kp LS(LC(LEFT))</t>
         </is>
       </c>
-      <c r="G62" s="7" t="inlineStr"/>
-      <c r="H62" s="7" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -8848,6 +9204,18 @@
         <is>
           <t>pos 29
 &amp;none</t>
+        </is>
+      </c>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N62" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -8888,6 +9256,12 @@
       </c>
       <c r="K63" s="9" t="inlineStr"/>
       <c r="L63" s="9" t="inlineStr"/>
+      <c r="M63" s="9" t="inlineStr"/>
+      <c r="N63" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
@@ -8897,41 +9271,31 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>pos 30
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>pos 31
-&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
           <t>pos 33
 &amp;none</t>
         </is>
       </c>
+      <c r="D64" s="7" t="inlineStr"/>
+      <c r="E64" s="7" t="inlineStr"/>
       <c r="F64" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G64" s="7" t="inlineStr"/>
-      <c r="H64" s="7" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;mo VIM_VISUAL_SYM</t>
         </is>
       </c>
+      <c r="H64" s="7" t="inlineStr"/>
       <c r="I64" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -8944,13 +9308,15 @@
 &amp;mo VIM_VISUAL_SYM</t>
         </is>
       </c>
-      <c r="K64" s="7" t="inlineStr">
+      <c r="K64" s="7" t="inlineStr"/>
+      <c r="L64" s="7" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L64" s="7" t="inlineStr">
+      <c r="N64" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -8964,20 +9330,16 @@
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr"/>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
+      <c r="C65" s="9" t="inlineStr"/>
       <c r="D65" s="9" t="inlineStr"/>
       <c r="E65" s="9" t="inlineStr"/>
       <c r="F65" s="9" t="inlineStr"/>
-      <c r="G65" s="9" t="inlineStr"/>
-      <c r="H65" s="9" t="inlineStr">
+      <c r="G65" s="9" t="inlineStr">
         <is>
           <t>&amp;mo VIM_VISUAL_SYM</t>
         </is>
       </c>
+      <c r="H65" s="9" t="inlineStr"/>
       <c r="I65" s="9" t="inlineStr"/>
       <c r="J65" s="9" t="inlineStr">
         <is>
@@ -8986,6 +9348,8 @@
       </c>
       <c r="K65" s="9" t="inlineStr"/>
       <c r="L65" s="9" t="inlineStr"/>
+      <c r="M65" s="9" t="inlineStr"/>
+      <c r="N65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -9003,7 +9367,9 @@
       <c r="I66" s="4" t="n"/>
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="4" t="n"/>
-      <c r="L66" s="5" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="n"/>
+      <c r="N66" s="5" t="n"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
@@ -9042,31 +9408,33 @@
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr"/>
-      <c r="H67" s="7" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr"/>
+      <c r="I67" s="7" t="inlineStr"/>
+      <c r="J67" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;mm_vim_visual_shift_6</t>
         </is>
       </c>
-      <c r="I67" s="7" t="inlineStr">
+      <c r="K67" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="J67" s="7" t="inlineStr">
+      <c r="L67" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="K67" s="7" t="inlineStr">
+      <c r="M67" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="L67" s="7" t="inlineStr">
+      <c r="N67" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp LS(HOME)</t>
@@ -9090,16 +9458,18 @@
       </c>
       <c r="F68" s="9" t="inlineStr"/>
       <c r="G68" s="9" t="inlineStr"/>
-      <c r="H68" s="10" t="inlineStr">
+      <c r="H68" s="9" t="inlineStr"/>
+      <c r="I68" s="9" t="inlineStr"/>
+      <c r="J68" s="10" t="inlineStr">
         <is>
           <t>mm_vim_visual_shift_6[0]
 ▸ &amp;none</t>
         </is>
       </c>
-      <c r="I68" s="9" t="inlineStr"/>
-      <c r="J68" s="9" t="inlineStr"/>
       <c r="K68" s="9" t="inlineStr"/>
-      <c r="L68" s="9" t="inlineStr">
+      <c r="L68" s="9" t="inlineStr"/>
+      <c r="M68" s="9" t="inlineStr"/>
+      <c r="N68" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LS(HOME)</t>
         </is>
@@ -9122,16 +9492,18 @@
       </c>
       <c r="F69" s="9" t="inlineStr"/>
       <c r="G69" s="9" t="inlineStr"/>
-      <c r="H69" s="10" t="inlineStr">
+      <c r="H69" s="9" t="inlineStr"/>
+      <c r="I69" s="9" t="inlineStr"/>
+      <c r="J69" s="10" t="inlineStr">
         <is>
           <t>mm_vim_visual_shift_6[1]
 ▸ &amp;kp LS(HOME)</t>
         </is>
       </c>
-      <c r="I69" s="9" t="inlineStr"/>
-      <c r="J69" s="9" t="inlineStr"/>
       <c r="K69" s="9" t="inlineStr"/>
-      <c r="L69" s="9" t="inlineStr">
+      <c r="L69" s="9" t="inlineStr"/>
+      <c r="M69" s="9" t="inlineStr"/>
+      <c r="N69" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -9174,31 +9546,33 @@
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr"/>
-      <c r="H70" s="7" t="inlineStr">
+      <c r="H70" s="7" t="inlineStr"/>
+      <c r="I70" s="7" t="inlineStr"/>
+      <c r="J70" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LS(LEFT)</t>
         </is>
       </c>
-      <c r="I70" s="7" t="inlineStr">
+      <c r="K70" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="J70" s="7" t="inlineStr">
+      <c r="L70" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="K70" s="7" t="inlineStr">
+      <c r="M70" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="L70" s="7" t="inlineStr">
+      <c r="N70" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -9221,15 +9595,17 @@
       <c r="E71" s="9" t="inlineStr"/>
       <c r="F71" s="9" t="inlineStr"/>
       <c r="G71" s="9" t="inlineStr"/>
-      <c r="H71" s="9" t="inlineStr">
+      <c r="H71" s="9" t="inlineStr"/>
+      <c r="I71" s="9" t="inlineStr"/>
+      <c r="J71" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LS(LEFT)</t>
         </is>
       </c>
-      <c r="I71" s="9" t="inlineStr"/>
-      <c r="J71" s="9" t="inlineStr"/>
       <c r="K71" s="9" t="inlineStr"/>
-      <c r="L71" s="9" t="inlineStr">
+      <c r="L71" s="9" t="inlineStr"/>
+      <c r="M71" s="9" t="inlineStr"/>
+      <c r="N71" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RCTRL</t>
         </is>
@@ -9271,13 +9647,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G72" s="7" t="inlineStr"/>
-      <c r="H72" s="7" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H72" s="7" t="inlineStr"/>
       <c r="I72" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -9300,6 +9676,18 @@
         <is>
           <t>pos 29
 &amp;none</t>
+        </is>
+      </c>
+      <c r="M72" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N72" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -9324,6 +9712,12 @@
       <c r="J73" s="9" t="inlineStr"/>
       <c r="K73" s="9" t="inlineStr"/>
       <c r="L73" s="9" t="inlineStr"/>
+      <c r="M73" s="9" t="inlineStr"/>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
@@ -9333,41 +9727,31 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>pos 30
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>pos 31
-&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
           <t>pos 33
 &amp;none</t>
         </is>
       </c>
+      <c r="D74" s="7" t="inlineStr"/>
+      <c r="E74" s="7" t="inlineStr"/>
       <c r="F74" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr"/>
-      <c r="H74" s="7" t="inlineStr">
+      <c r="G74" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
+      <c r="H74" s="7" t="inlineStr"/>
       <c r="I74" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -9380,13 +9764,15 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="K74" s="7" t="inlineStr">
+      <c r="K74" s="7" t="inlineStr"/>
+      <c r="L74" s="7" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L74" s="7" t="inlineStr">
+      <c r="N74" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -9400,11 +9786,7 @@
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr"/>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
+      <c r="C75" s="9" t="inlineStr"/>
       <c r="D75" s="9" t="inlineStr"/>
       <c r="E75" s="9" t="inlineStr"/>
       <c r="F75" s="9" t="inlineStr"/>
@@ -9414,6 +9796,8 @@
       <c r="J75" s="9" t="inlineStr"/>
       <c r="K75" s="9" t="inlineStr"/>
       <c r="L75" s="9" t="inlineStr"/>
+      <c r="M75" s="9" t="inlineStr"/>
+      <c r="N75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -9431,7 +9815,9 @@
       <c r="I76" s="4" t="n"/>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
-      <c r="L76" s="5" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="5" t="n"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
@@ -9470,31 +9856,33 @@
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr"/>
-      <c r="H77" s="7" t="inlineStr">
+      <c r="H77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp F6</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
+      <c r="K77" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp F7</t>
         </is>
       </c>
-      <c r="J77" s="7" t="inlineStr">
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp F8</t>
         </is>
       </c>
-      <c r="K77" s="7" t="inlineStr">
+      <c r="M77" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp F9</t>
         </is>
       </c>
-      <c r="L77" s="7" t="inlineStr">
+      <c r="N77" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp F10</t>
@@ -9533,27 +9921,29 @@
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr"/>
-      <c r="H78" s="9" t="inlineStr">
+      <c r="H78" s="9" t="inlineStr"/>
+      <c r="I78" s="9" t="inlineStr"/>
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F6</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
+      <c r="K78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F7</t>
         </is>
       </c>
-      <c r="J78" s="9" t="inlineStr">
+      <c r="L78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F8</t>
         </is>
       </c>
-      <c r="K78" s="9" t="inlineStr">
+      <c r="M78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F9</t>
         </is>
       </c>
-      <c r="L78" s="9" t="inlineStr">
+      <c r="N78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F10</t>
         </is>
@@ -9596,31 +9986,33 @@
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
-      <c r="H79" s="7" t="inlineStr">
+      <c r="H79" s="7" t="inlineStr"/>
+      <c r="I79" s="7" t="inlineStr"/>
+      <c r="J79" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
+      <c r="K79" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="J79" s="7" t="inlineStr">
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="K79" s="7" t="inlineStr">
+      <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="L79" s="7" t="inlineStr">
+      <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
@@ -9646,12 +10038,14 @@
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
       <c r="J80" s="9" t="inlineStr"/>
-      <c r="K80" s="9" t="inlineStr">
+      <c r="K80" s="9" t="inlineStr"/>
+      <c r="L80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr">
         <is>
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="L80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr"/>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -9689,13 +10083,13 @@
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H81" s="7" t="inlineStr"/>
       <c r="I81" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -9717,6 +10111,18 @@
       <c r="L81" s="7" t="inlineStr">
         <is>
           <t>pos 29
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N81" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
@@ -9746,6 +10152,8 @@
       </c>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
+      <c r="M82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -9755,41 +10163,31 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>pos 30
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
           <t>pos 33
 &amp;none</t>
         </is>
       </c>
+      <c r="D83" s="7" t="inlineStr"/>
+      <c r="E83" s="7" t="inlineStr"/>
       <c r="F83" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G83" s="7" t="inlineStr"/>
-      <c r="H83" s="7" t="inlineStr">
+      <c r="G83" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
+      <c r="H83" s="7" t="inlineStr"/>
       <c r="I83" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -9802,13 +10200,15 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="K83" s="7" t="inlineStr">
+      <c r="K83" s="7" t="inlineStr"/>
+      <c r="L83" s="7" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L83" s="7" t="inlineStr">
+      <c r="N83" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -9832,6 +10232,8 @@
       <c r="J84" s="9" t="inlineStr"/>
       <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr"/>
+      <c r="M84" s="9" t="inlineStr"/>
+      <c r="N84" s="9" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -9849,7 +10251,9 @@
       <c r="I85" s="4" t="n"/>
       <c r="J85" s="4" t="n"/>
       <c r="K85" s="4" t="n"/>
-      <c r="L85" s="5" t="n"/>
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="4" t="n"/>
+      <c r="N85" s="5" t="n"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
@@ -9888,31 +10292,33 @@
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr"/>
-      <c r="H86" s="7" t="inlineStr">
+      <c r="H86" s="7" t="inlineStr"/>
+      <c r="I86" s="7" t="inlineStr"/>
+      <c r="J86" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;none</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
+      <c r="K86" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;out OUT_USB</t>
         </is>
       </c>
-      <c r="J86" s="7" t="inlineStr">
+      <c r="L86" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="K86" s="7" t="inlineStr">
+      <c r="M86" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="L86" s="7" t="inlineStr">
+      <c r="N86" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -9952,14 +10358,16 @@
       </c>
       <c r="G87" s="9" t="inlineStr"/>
       <c r="H87" s="9" t="inlineStr"/>
-      <c r="I87" s="9" t="inlineStr">
+      <c r="I87" s="9" t="inlineStr"/>
+      <c r="J87" s="9" t="inlineStr"/>
+      <c r="K87" s="9" t="inlineStr">
         <is>
           <t>&amp;out OUT_USB</t>
         </is>
       </c>
-      <c r="J87" s="9" t="inlineStr"/>
-      <c r="K87" s="9" t="inlineStr"/>
       <c r="L87" s="9" t="inlineStr"/>
+      <c r="M87" s="9" t="inlineStr"/>
+      <c r="N87" s="9" t="inlineStr"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
@@ -9998,31 +10406,33 @@
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr"/>
-      <c r="H88" s="7" t="inlineStr">
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr"/>
+      <c r="J88" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
+      <c r="K88" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="J88" s="7" t="inlineStr">
+      <c r="L88" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="K88" s="7" t="inlineStr">
+      <c r="M88" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="L88" s="7" t="inlineStr">
+      <c r="N88" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
@@ -10050,6 +10460,8 @@
       <c r="J89" s="9" t="inlineStr"/>
       <c r="K89" s="9" t="inlineStr"/>
       <c r="L89" s="9" t="inlineStr"/>
+      <c r="M89" s="9" t="inlineStr"/>
+      <c r="N89" s="9" t="inlineStr"/>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
@@ -10087,13 +10499,13 @@
 &amp;out OUT_BLE</t>
         </is>
       </c>
-      <c r="G90" s="7" t="inlineStr"/>
-      <c r="H90" s="7" t="inlineStr">
+      <c r="G90" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H90" s="7" t="inlineStr"/>
       <c r="I90" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -10115,6 +10527,18 @@
       <c r="L90" s="7" t="inlineStr">
         <is>
           <t>pos 29
+&amp;none</t>
+        </is>
+      </c>
+      <c r="M90" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N90" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
 &amp;none</t>
         </is>
       </c>
@@ -10144,6 +10568,8 @@
       <c r="J91" s="9" t="inlineStr"/>
       <c r="K91" s="9" t="inlineStr"/>
       <c r="L91" s="9" t="inlineStr"/>
+      <c r="M91" s="9" t="inlineStr"/>
+      <c r="N91" s="9" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
@@ -10153,41 +10579,31 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>pos 30
+          <t>pos 32
 &amp;none</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>pos 31
-&amp;none</t>
-        </is>
-      </c>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>pos 32
-&amp;none</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
           <t>pos 33
 &amp;none</t>
         </is>
       </c>
+      <c r="D92" s="7" t="inlineStr"/>
+      <c r="E92" s="7" t="inlineStr"/>
       <c r="F92" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G92" s="7" t="inlineStr"/>
-      <c r="H92" s="7" t="inlineStr">
+      <c r="G92" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
+      <c r="H92" s="7" t="inlineStr"/>
       <c r="I92" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -10200,13 +10616,15 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="K92" s="7" t="inlineStr">
+      <c r="K92" s="7" t="inlineStr"/>
+      <c r="L92" s="7" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L92" s="7" t="inlineStr">
+      <c r="N92" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -10230,6 +10648,8 @@
       <c r="J93" s="9" t="inlineStr"/>
       <c r="K93" s="9" t="inlineStr"/>
       <c r="L93" s="9" t="inlineStr"/>
+      <c r="M93" s="9" t="inlineStr"/>
+      <c r="N93" s="9" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -10247,7 +10667,9 @@
       <c r="I94" s="4" t="n"/>
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="n"/>
-      <c r="L94" s="5" t="n"/>
+      <c r="L94" s="4" t="n"/>
+      <c r="M94" s="4" t="n"/>
+      <c r="N94" s="5" t="n"/>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
@@ -10286,31 +10708,33 @@
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr"/>
-      <c r="H95" s="7" t="inlineStr">
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;none</t>
         </is>
       </c>
-      <c r="I95" s="7" t="inlineStr">
+      <c r="K95" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="J95" s="7" t="inlineStr">
+      <c r="L95" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="K95" s="7" t="inlineStr">
+      <c r="M95" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="L95" s="7" t="inlineStr">
+      <c r="N95" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -10334,6 +10758,8 @@
       <c r="J96" s="9" t="inlineStr"/>
       <c r="K96" s="9" t="inlineStr"/>
       <c r="L96" s="9" t="inlineStr"/>
+      <c r="M96" s="9" t="inlineStr"/>
+      <c r="N96" s="9" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
@@ -10372,31 +10798,33 @@
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr"/>
-      <c r="H97" s="7" t="inlineStr">
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr"/>
+      <c r="J97" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="I97" s="7" t="inlineStr">
+      <c r="K97" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="J97" s="7" t="inlineStr">
+      <c r="L97" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
-      <c r="K97" s="7" t="inlineStr">
+      <c r="M97" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="L97" s="7" t="inlineStr">
+      <c r="N97" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;trans</t>
@@ -10425,14 +10853,16 @@
       <c r="G98" s="9" t="inlineStr"/>
       <c r="H98" s="9" t="inlineStr"/>
       <c r="I98" s="9" t="inlineStr"/>
-      <c r="J98" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mo MOUSE_SCROLL</t>
-        </is>
-      </c>
+      <c r="J98" s="9" t="inlineStr"/>
       <c r="K98" s="9" t="inlineStr"/>
       <c r="L98" s="9" t="inlineStr">
         <is>
+          <t>&amp;mo MOUSE_SCROLL</t>
+        </is>
+      </c>
+      <c r="M98" s="9" t="inlineStr"/>
+      <c r="N98" s="9" t="inlineStr">
+        <is>
           <t>▽</t>
         </is>
       </c>
@@ -10473,13 +10903,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G99" s="7" t="inlineStr"/>
-      <c r="H99" s="7" t="inlineStr">
+      <c r="G99" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -10502,6 +10932,18 @@
         <is>
           <t>pos 29
 &amp;none</t>
+        </is>
+      </c>
+      <c r="M99" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;none</t>
+        </is>
+      </c>
+      <c r="N99" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;trans</t>
         </is>
       </c>
     </row>
@@ -10526,6 +10968,12 @@
       <c r="J100" s="9" t="inlineStr"/>
       <c r="K100" s="9" t="inlineStr"/>
       <c r="L100" s="9" t="inlineStr"/>
+      <c r="M100" s="9" t="inlineStr"/>
+      <c r="N100" s="9" t="inlineStr">
+        <is>
+          <t>▽</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
@@ -10535,41 +10983,31 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>pos 30
-&amp;none</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;trans</t>
-        </is>
-      </c>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
           <t>pos 32
 &amp;trans</t>
         </is>
       </c>
-      <c r="E101" s="7" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;trans</t>
         </is>
       </c>
+      <c r="D101" s="7" t="inlineStr"/>
+      <c r="E101" s="7" t="inlineStr"/>
       <c r="F101" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G101" s="7" t="inlineStr"/>
-      <c r="H101" s="7" t="inlineStr">
+      <c r="G101" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
+      <c r="H101" s="7" t="inlineStr"/>
       <c r="I101" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -10582,13 +11020,15 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="K101" s="7" t="inlineStr">
+      <c r="K101" s="7" t="inlineStr"/>
+      <c r="L101" s="7" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L101" s="7" t="inlineStr">
+      <c r="N101" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -10601,22 +11041,18 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B102" s="9" t="inlineStr"/>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>▽</t>
+        </is>
+      </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
-      <c r="E102" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="D102" s="9" t="inlineStr"/>
+      <c r="E102" s="9" t="inlineStr"/>
       <c r="F102" s="9" t="inlineStr"/>
       <c r="G102" s="9" t="inlineStr"/>
       <c r="H102" s="9" t="inlineStr"/>
@@ -10624,6 +11060,8 @@
       <c r="J102" s="9" t="inlineStr"/>
       <c r="K102" s="9" t="inlineStr"/>
       <c r="L102" s="9" t="inlineStr"/>
+      <c r="M102" s="9" t="inlineStr"/>
+      <c r="N102" s="9" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -10641,7 +11079,9 @@
       <c r="I103" s="4" t="n"/>
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="4" t="n"/>
-      <c r="L103" s="5" t="n"/>
+      <c r="L103" s="4" t="n"/>
+      <c r="M103" s="4" t="n"/>
+      <c r="N103" s="5" t="n"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
@@ -10680,31 +11120,33 @@
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr"/>
-      <c r="H104" s="7" t="inlineStr">
+      <c r="H104" s="7" t="inlineStr"/>
+      <c r="I104" s="7" t="inlineStr"/>
+      <c r="J104" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;none</t>
         </is>
       </c>
-      <c r="I104" s="7" t="inlineStr">
+      <c r="K104" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="J104" s="7" t="inlineStr">
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="K104" s="7" t="inlineStr">
+      <c r="M104" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="L104" s="7" t="inlineStr">
+      <c r="N104" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -10728,6 +11170,8 @@
       <c r="J105" s="9" t="inlineStr"/>
       <c r="K105" s="9" t="inlineStr"/>
       <c r="L105" s="9" t="inlineStr"/>
+      <c r="M105" s="9" t="inlineStr"/>
+      <c r="N105" s="9" t="inlineStr"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
@@ -10766,31 +11210,33 @@
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr"/>
-      <c r="H106" s="7" t="inlineStr">
+      <c r="H106" s="7" t="inlineStr"/>
+      <c r="I106" s="7" t="inlineStr"/>
+      <c r="J106" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="I106" s="7" t="inlineStr">
+      <c r="K106" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;mkp MB1</t>
         </is>
       </c>
-      <c r="J106" s="7" t="inlineStr">
+      <c r="L106" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="K106" s="7" t="inlineStr">
+      <c r="M106" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;mkp MB2</t>
         </is>
       </c>
-      <c r="L106" s="7" t="inlineStr">
+      <c r="N106" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -10822,18 +11268,20 @@
       <c r="F107" s="9" t="inlineStr"/>
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
-      <c r="I107" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mkp MB1</t>
-        </is>
-      </c>
+      <c r="I107" s="9" t="inlineStr"/>
       <c r="J107" s="9" t="inlineStr"/>
       <c r="K107" s="9" t="inlineStr">
         <is>
+          <t>&amp;mkp MB1</t>
+        </is>
+      </c>
+      <c r="L107" s="9" t="inlineStr"/>
+      <c r="M107" s="9" t="inlineStr">
+        <is>
           <t>&amp;mkp MB2</t>
         </is>
       </c>
-      <c r="L107" s="9" t="inlineStr">
+      <c r="N107" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RCTRL</t>
         </is>
@@ -10875,13 +11323,13 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="G108" s="7" t="inlineStr"/>
-      <c r="H108" s="7" t="inlineStr">
+      <c r="G108" s="7" t="inlineStr">
         <is>
           <t>pos 25
 &amp;none</t>
         </is>
       </c>
+      <c r="H108" s="7" t="inlineStr"/>
       <c r="I108" s="7" t="inlineStr">
         <is>
           <t>pos 26
@@ -10904,6 +11352,18 @@
         <is>
           <t>pos 29
 &amp;none</t>
+        </is>
+      </c>
+      <c r="M108" s="7" t="inlineStr">
+        <is>
+          <t>pos 30
+&amp;mkp MB5</t>
+        </is>
+      </c>
+      <c r="N108" s="7" t="inlineStr">
+        <is>
+          <t>pos 31
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -10940,6 +11400,16 @@
         </is>
       </c>
       <c r="L109" s="9" t="inlineStr"/>
+      <c r="M109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB5</t>
+        </is>
+      </c>
+      <c r="N109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -10949,41 +11419,31 @@
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>pos 30
-&amp;mkp MB5</t>
-        </is>
-      </c>
-      <c r="C110" s="7" t="inlineStr">
-        <is>
-          <t>pos 31
-&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="inlineStr">
-        <is>
           <t>pos 32
 &amp;kp LEFT_WIN</t>
         </is>
       </c>
-      <c r="E110" s="7" t="inlineStr">
+      <c r="C110" s="7" t="inlineStr">
         <is>
           <t>pos 33
 &amp;kp LEFT_ALT</t>
         </is>
       </c>
+      <c r="D110" s="7" t="inlineStr"/>
+      <c r="E110" s="7" t="inlineStr"/>
       <c r="F110" s="7" t="inlineStr">
         <is>
           <t>pos 34
 &amp;none</t>
         </is>
       </c>
-      <c r="G110" s="7" t="inlineStr"/>
-      <c r="H110" s="7" t="inlineStr">
+      <c r="G110" s="7" t="inlineStr">
         <is>
           <t>pos 35
 &amp;none</t>
         </is>
       </c>
+      <c r="H110" s="7" t="inlineStr"/>
       <c r="I110" s="7" t="inlineStr">
         <is>
           <t>pos 36
@@ -10996,13 +11456,15 @@
 &amp;none</t>
         </is>
       </c>
-      <c r="K110" s="7" t="inlineStr">
+      <c r="K110" s="7" t="inlineStr"/>
+      <c r="L110" s="7" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr">
         <is>
           <t>pos 38
 &amp;none</t>
         </is>
       </c>
-      <c r="L110" s="7" t="inlineStr">
+      <c r="N110" s="7" t="inlineStr">
         <is>
           <t>pos 39
 &amp;none</t>
@@ -11017,24 +11479,16 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>&amp;mkp MB5</t>
+          <t>&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp RIGHT_SHIFT</t>
-        </is>
-      </c>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp LEFT_WIN</t>
-        </is>
-      </c>
-      <c r="E111" s="9" t="inlineStr">
-        <is>
           <t>&amp;kp LEFT_ALT</t>
         </is>
       </c>
+      <c r="D111" s="9" t="inlineStr"/>
+      <c r="E111" s="9" t="inlineStr"/>
       <c r="F111" s="9" t="inlineStr"/>
       <c r="G111" s="9" t="inlineStr"/>
       <c r="H111" s="9" t="inlineStr"/>
@@ -11042,19 +11496,21 @@
       <c r="J111" s="9" t="inlineStr"/>
       <c r="K111" s="9" t="inlineStr"/>
       <c r="L111" s="9" t="inlineStr"/>
+      <c r="M111" s="9" t="inlineStr"/>
+      <c r="N111" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A16:L16"/>
-    <mergeCell ref="A76:L76"/>
-    <mergeCell ref="A85:L85"/>
-    <mergeCell ref="A45:L45"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A94:L94"/>
-    <mergeCell ref="A103:L103"/>
-    <mergeCell ref="A66:L66"/>
-    <mergeCell ref="A55:L55"/>
-    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A55:N55"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A45:N45"/>
+    <mergeCell ref="A16:N16"/>
+    <mergeCell ref="A76:N76"/>
+    <mergeCell ref="A85:N85"/>
+    <mergeCell ref="A28:N28"/>
+    <mergeCell ref="A103:N103"/>
+    <mergeCell ref="A66:N66"/>
+    <mergeCell ref="A94:N94"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -4440,7 +4440,7 @@
       <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp CAPSLOCK</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -4452,19 +4452,19 @@
       <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
@@ -4497,7 +4497,7 @@
       <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
     </row>
@@ -4507,15 +4507,31 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr"/>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>CAPSLOCK</t>
+        </is>
+      </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
           <t>リセット</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="inlineStr"/>
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
@@ -4527,7 +4543,11 @@
           <t>リセット</t>
         </is>
       </c>
-      <c r="N80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -4538,7 +4558,7 @@
       <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -4550,7 +4570,7 @@
       <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -4605,7 +4625,7 @@
       <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 31
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
     </row>
@@ -4615,9 +4635,17 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>K_APP</t>
+        </is>
+      </c>
       <c r="C82" s="9" t="inlineStr"/>
-      <c r="D82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
       <c r="E82" s="9" t="inlineStr"/>
       <c r="F82" s="9" t="inlineStr">
         <is>
@@ -4635,7 +4663,11 @@
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
-      <c r="N82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -9958,7 +9990,7 @@
       <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp CAPSLOCK</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -9970,19 +10002,19 @@
       <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
@@ -10015,7 +10047,7 @@
       <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
     </row>
@@ -10025,15 +10057,31 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr"/>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp CAPSLOCK</t>
+        </is>
+      </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="inlineStr"/>
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
@@ -10045,7 +10093,11 @@
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="N80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F11</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -10056,7 +10108,7 @@
       <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -10068,7 +10120,7 @@
       <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -10123,7 +10175,7 @@
       <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 31
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
     </row>
@@ -10133,9 +10185,17 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp K_APP</t>
+        </is>
+      </c>
       <c r="C82" s="9" t="inlineStr"/>
-      <c r="D82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp INSERT</t>
+        </is>
+      </c>
       <c r="E82" s="9" t="inlineStr"/>
       <c r="F82" s="9" t="inlineStr">
         <is>
@@ -10153,7 +10213,11 @@
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
-      <c r="N82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F12</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -4440,13 +4440,13 @@
       <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp CAPSLOCK</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4491,7 +4491,7 @@
       <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
@@ -4507,16 +4507,8 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>CAPSLOCK</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
+      <c r="B80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
       <c r="D80" s="9" t="inlineStr">
         <is>
           <t>PRINTSCREEN</t>
@@ -4538,11 +4530,7 @@
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr"/>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
+      <c r="M80" s="9" t="inlineStr"/>
       <c r="N80" s="9" t="inlineStr">
         <is>
           <t>F11</t>
@@ -4582,7 +4570,7 @@
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -4601,7 +4589,7 @@
       <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 27
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -4647,19 +4635,11 @@
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="F82" s="9" t="inlineStr"/>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
       <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
@@ -9990,13 +9970,13 @@
       <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp CAPSLOCK</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -10041,7 +10021,7 @@
       <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
@@ -10057,16 +10037,8 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp CAPSLOCK</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
+      <c r="B80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
       <c r="D80" s="9" t="inlineStr">
         <is>
           <t>&amp;kp PRINTSCREEN</t>
@@ -10088,11 +10060,7 @@
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr"/>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
+      <c r="M80" s="9" t="inlineStr"/>
       <c r="N80" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F11</t>
@@ -10132,7 +10100,7 @@
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -10151,7 +10119,7 @@
       <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 27
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -10197,19 +10165,11 @@
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="F82" s="9" t="inlineStr"/>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
       <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -4446,25 +4446,25 @@
       <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
@@ -4491,13 +4491,13 @@
       <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
     </row>
@@ -4508,26 +4508,34 @@
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr"/>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="inlineStr"/>
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr"/>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
-      <c r="N80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -4538,7 +4546,7 @@
       <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -4550,7 +4558,7 @@
       <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -4562,7 +4570,7 @@
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -4581,7 +4589,7 @@
       <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 27
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -4605,7 +4613,7 @@
       <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 31
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
     </row>
@@ -4615,27 +4623,31 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>K_APP</t>
+        </is>
+      </c>
       <c r="C82" s="9" t="inlineStr"/>
-      <c r="D82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
       <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="F82" s="9" t="inlineStr"/>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
       <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
-      <c r="N82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -9964,25 +9976,25 @@
       <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
@@ -10009,13 +10021,13 @@
       <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
     </row>
@@ -10026,26 +10038,34 @@
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr"/>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="inlineStr"/>
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr"/>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
-      <c r="N80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F11</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -10056,7 +10076,7 @@
       <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -10068,7 +10088,7 @@
       <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -10080,7 +10100,7 @@
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -10099,7 +10119,7 @@
       <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 27
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -10123,7 +10143,7 @@
       <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 31
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
     </row>
@@ -10133,27 +10153,31 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp K_APP</t>
+        </is>
+      </c>
       <c r="C82" s="9" t="inlineStr"/>
-      <c r="D82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp INSERT</t>
+        </is>
+      </c>
       <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="F82" s="9" t="inlineStr"/>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
       <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
-      <c r="N82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F12</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
